--- a/cypress/downloads/Plataforma externa Volta Redonda.xlsx
+++ b/cypress/downloads/Plataforma externa Volta Redonda.xlsx
@@ -269,40 +269,43 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">CUPOM10 2</t>
+          <t xml:space="preserve">DIA23JUNHO</t>
         </is>
       </c>
       <c r="B3" s="56">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">CUPOM10</t>
-        </is>
+          <t xml:space="preserve">DIA23JUNHO</t>
+        </is>
+      </c>
+      <c t="n" r="D3">
+        <v>100</v>
       </c>
       <c t="n" r="E3">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">09/06/2025 00:00:00</t>
+          <t xml:space="preserve">23/06/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">30/06/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">cupomhoje</t>
+          <t xml:space="preserve">Teste2306</t>
         </is>
       </c>
       <c r="B4" s="56">
@@ -310,23 +313,23 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">cupom17</t>
+          <t xml:space="preserve">teste2306</t>
         </is>
       </c>
       <c t="n" r="D4">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c t="n" r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">17/06/2025 08:00:00</t>
+          <t xml:space="preserve">23/06/2025 15:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">20/06/2025 09:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
@@ -338,111 +341,114 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">testecupom17</t>
+          <t xml:space="preserve">dia17</t>
         </is>
       </c>
       <c r="B5" s="56">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">testecupom17</t>
+          <t xml:space="preserve">dia17</t>
         </is>
       </c>
       <c t="n" r="D5">
         <v>100</v>
       </c>
       <c t="n" r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">17/06/2025 08:00:00</t>
+          <t xml:space="preserve">17/07/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">26/06/2025 09:25:00</t>
+          <t xml:space="preserve">17/07/2025 19:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65">
-        <v>1706</v>
+      <c t="inlineStr" r="A6">
+        <is>
+          <t xml:space="preserve">teste08/08</t>
+        </is>
       </c>
       <c r="B6" s="56">
         <v>0.1</v>
       </c>
-      <c r="C6" s="65">
-        <v>1706</v>
+      <c t="inlineStr" r="C6">
+        <is>
+          <t xml:space="preserve">teste08/08</t>
+        </is>
       </c>
       <c t="n" r="D6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c t="n" r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">17/06/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">17/06/2025 17:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 10.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">DIA23JUNHO</t>
-        </is>
-      </c>
-      <c r="B7" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">testecupom</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B7">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">DIA23JUNHO</t>
-        </is>
-      </c>
-      <c t="n" r="D7">
-        <v>100</v>
+          <t xml:space="preserve">testecupom</t>
+        </is>
       </c>
       <c t="n" r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t xml:space="preserve">23/06/2025 08:00:00</t>
+          <t xml:space="preserve">20/08/2025 09:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">30/06/2025 08:00:00</t>
+          <t xml:space="preserve">22/08/2025 11:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">Teste2306</t>
+          <t xml:space="preserve">testecupom21/08</t>
         </is>
       </c>
       <c r="B8" s="56">
@@ -450,18 +456,15 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">teste2306</t>
-        </is>
-      </c>
-      <c t="n" r="D8">
-        <v>11</v>
+          <t xml:space="preserve">testecupom21/08</t>
+        </is>
       </c>
       <c t="n" r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">23/06/2025 15:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G8">
@@ -478,55 +481,50 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">dia17</t>
+          <t xml:space="preserve">Cupom7</t>
         </is>
       </c>
       <c r="B9" s="56">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">dia17</t>
+          <t xml:space="preserve">0712</t>
         </is>
       </c>
       <c t="n" r="D9">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c t="n" r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">17/07/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">17/07/2025 19:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">teste08/08</t>
+          <t xml:space="preserve">CUPOM TESTE</t>
         </is>
       </c>
       <c r="B10" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C10">
-        <is>
-          <t xml:space="preserve">teste08/08</t>
-        </is>
-      </c>
-      <c t="n" r="D10">
-        <v>100</v>
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="65">
+        <v>1010</v>
       </c>
       <c t="n" r="E10">
         <v>1</v>
@@ -543,14 +541,14 @@
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">testecupom</t>
+          <t xml:space="preserve">Testecupom</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
@@ -560,20 +558,23 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">testecupom</t>
-        </is>
+          <t xml:space="preserve">Testecupom</t>
+        </is>
+      </c>
+      <c t="n" r="D11">
+        <v>50</v>
       </c>
       <c t="n" r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">20/08/2025 09:25:00</t>
+          <t xml:space="preserve">23/09/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">22/08/2025 11:30:00</t>
+          <t xml:space="preserve">26/09/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
@@ -585,19 +586,19 @@
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">testecupom21/08</t>
-        </is>
-      </c>
-      <c r="B12" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C12">
-        <is>
-          <t xml:space="preserve">testecupom21/08</t>
-        </is>
+          <t xml:space="preserve">TESTE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B12">
+        <is>
+          <t xml:space="preserve">R$ 60.00</t>
+        </is>
+      </c>
+      <c r="C12" s="65">
+        <v>606060</v>
       </c>
       <c t="n" r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
@@ -618,19 +619,14 @@
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">Cupom7</t>
+          <t xml:space="preserve">TESTE</t>
         </is>
       </c>
       <c r="B13" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C13">
-        <is>
-          <t xml:space="preserve">0712</t>
-        </is>
-      </c>
-      <c t="n" r="D13">
-        <v>8</v>
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="65">
+        <v>505050</v>
       </c>
       <c t="n" r="E13">
         <v>3</v>
@@ -654,14 +650,14 @@
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">CUPOM TESTE</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B14" s="56">
         <v>0.5</v>
       </c>
       <c r="C14" s="65">
-        <v>1010</v>
+        <v>4040</v>
       </c>
       <c t="n" r="E14">
         <v>1</v>
@@ -685,7 +681,7 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">Testecupom</t>
+          <t xml:space="preserve">teste2609</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
@@ -695,23 +691,23 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Testecupom</t>
+          <t xml:space="preserve">teste2609</t>
         </is>
       </c>
       <c t="n" r="D15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c t="n" r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">23/09/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">26/09/2025 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
@@ -723,28 +719,33 @@
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">TESTE</t>
+          <t xml:space="preserve">testecupom10/10</t>
         </is>
       </c>
       <c t="inlineStr" r="B16">
         <is>
-          <t xml:space="preserve">R$ 60.00</t>
-        </is>
-      </c>
-      <c r="C16" s="65">
-        <v>606060</v>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">testecupom10/10</t>
+        </is>
+      </c>
+      <c t="n" r="D16">
+        <v>100</v>
       </c>
       <c t="n" r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">10/10/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">11/10/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
@@ -756,17 +757,22 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">TESTE</t>
+          <t xml:space="preserve">cupom14/10</t>
         </is>
       </c>
       <c r="B17" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="65">
-        <v>505050</v>
+        <v>0.1</v>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">cupom14/10</t>
+        </is>
+      </c>
+      <c t="n" r="D17">
+        <v>100</v>
       </c>
       <c t="n" r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F17">
         <is>
@@ -787,14 +793,14 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">Cupom50</t>
         </is>
       </c>
       <c r="B18" s="56">
         <v>0.5</v>
       </c>
       <c r="C18" s="65">
-        <v>4040</v>
+        <v>3110</v>
       </c>
       <c t="n" r="E18">
         <v>1</v>
@@ -818,98 +824,87 @@
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">teste2609</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B19">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C19">
-        <is>
-          <t xml:space="preserve">teste2609</t>
-        </is>
+          <t xml:space="preserve">Teste12/11</t>
+        </is>
+      </c>
+      <c r="B19" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="65">
+        <v>105</v>
       </c>
       <c t="n" r="D19">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c t="n" r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">testecupom10/10</t>
+          <t xml:space="preserve">TESTE12/11</t>
         </is>
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C20">
-        <is>
-          <t xml:space="preserve">testecupom10/10</t>
-        </is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C20" s="65">
+        <v>201</v>
       </c>
       <c t="n" r="D20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">10/10/2025 08:00:00</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">11/10/2025 14:00:00</t>
+          <t xml:space="preserve">01/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">cupom14/10</t>
+          <t xml:space="preserve">cupom502</t>
         </is>
       </c>
       <c r="B21" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C21">
-        <is>
-          <t xml:space="preserve">cupom14/10</t>
-        </is>
-      </c>
-      <c t="n" r="D21">
-        <v>100</v>
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="65">
+        <v>5486</v>
       </c>
       <c t="n" r="E21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F21">
         <is>
@@ -930,26 +925,29 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Cupom50</t>
+          <t xml:space="preserve">TESTE12/11</t>
         </is>
       </c>
       <c r="B22" s="56">
         <v>0.5</v>
       </c>
       <c r="C22" s="65">
-        <v>3110</v>
+        <v>47992458811</v>
+      </c>
+      <c t="n" r="D22">
+        <v>100</v>
       </c>
       <c t="n" r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/01/2026 07:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
@@ -961,87 +959,89 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Teste12/11</t>
+          <t xml:space="preserve">Teste</t>
         </is>
       </c>
       <c r="B23" s="56">
         <v>0.5</v>
       </c>
       <c r="C23" s="65">
-        <v>105</v>
+        <v>1617</v>
       </c>
       <c t="n" r="D23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c t="n" r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">12/11/2025 16:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">01/03/2026 00:00:00</t>
+          <t xml:space="preserve">12/11/2025 16:20:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
+          <t xml:space="preserve">Testeeeee</t>
         </is>
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
       <c r="C24" s="65">
-        <v>201</v>
+        <v>2222</v>
       </c>
       <c t="n" r="D24">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c t="n" r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">01/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">cupom502</t>
+          <t xml:space="preserve">Teste17/11</t>
         </is>
       </c>
       <c r="B25" s="56">
         <v>0.5</v>
       </c>
-      <c r="C25" s="65">
-        <v>5486</v>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Teste17/11</t>
+        </is>
       </c>
       <c t="n" r="E25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
@@ -1062,63 +1062,65 @@
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B26" s="56">
         <v>0.5</v>
       </c>
       <c r="C26" s="65">
-        <v>47992458811</v>
+        <v>5050</v>
       </c>
       <c t="n" r="D26">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c t="n" r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">21/11/2025 14:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
         <is>
-          <t xml:space="preserve">03/01/2026 07:35:00</t>
+          <t xml:space="preserve">21/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B27" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c r="C27" s="65">
-        <v>1617</v>
+        <v>123</v>
       </c>
       <c t="n" r="D27">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c t="n" r="E27">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">12/11/2025 16:15:00</t>
+          <t xml:space="preserve">18/11/2025 13:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">12/11/2025 16:20:00</t>
+          <t xml:space="preserve">19/11/2025 14:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
@@ -1130,31 +1132,31 @@
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">Testeeeee</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B28">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c r="C28" s="65">
-        <v>2222</v>
+          <t xml:space="preserve">testes 2111</t>
+        </is>
+      </c>
+      <c r="B28" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">date123</t>
+        </is>
       </c>
       <c t="n" r="D28">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c t="n" r="E28">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">18/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">19/11/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
@@ -1166,98 +1168,104 @@
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Teste17/11</t>
-        </is>
-      </c>
-      <c r="B29" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 04/12-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Teste17/11</t>
-        </is>
+          <t xml:space="preserve">Teste 04/12-1</t>
+        </is>
+      </c>
+      <c t="n" r="D29">
+        <v>1</v>
       </c>
       <c t="n" r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">04/12/2025 10:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">04/12/2025 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c r="B30" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C30" s="65">
-        <v>5050</v>
-      </c>
-      <c t="n" r="D30">
-        <v>10</v>
+          <t xml:space="preserve">TesteDois</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">TesteDois</t>
+        </is>
       </c>
       <c t="n" r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">21/11/2025 14:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">21/11/2025 15:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B31">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c r="C31" s="65">
-        <v>123</v>
+          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
+        </is>
+      </c>
+      <c r="B31" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">limitado</t>
+        </is>
       </c>
       <c t="n" r="D31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">18/11/2025 13:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">19/11/2025 14:50:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
@@ -1269,31 +1277,30 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">testes 2111</t>
-        </is>
-      </c>
-      <c r="B32" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">date123</t>
-        </is>
-      </c>
-      <c t="n" r="D32">
-        <v>5</v>
+          <t xml:space="preserve">acabou50</t>
+        </is>
       </c>
       <c t="n" r="E32">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">18/11/2025 15:55:00</t>
+          <t xml:space="preserve">04/12/2025 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">19/11/2025 19:55:00</t>
+          <t xml:space="preserve">05/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
@@ -1305,17 +1312,15 @@
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B33">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">cupom teste % 08/12/2025</t>
+        </is>
+      </c>
+      <c r="B33" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
+          <t xml:space="preserve">08122025</t>
         </is>
       </c>
       <c t="n" r="D33">
@@ -1326,32 +1331,34 @@
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">04/12/2025 10:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">04/12/2025 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">cupom 04/12 data vencida</t>
-        </is>
-      </c>
-      <c r="B34" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">caio5050</t>
+          <t xml:space="preserve">0802200511</t>
         </is>
       </c>
       <c t="n" r="E34">
@@ -1359,12 +1366,12 @@
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">04/12/2025 00:00:00</t>
+          <t xml:space="preserve">01/12/2025 04:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">04/12/2025 13:00:00</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
@@ -1376,30 +1383,31 @@
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">TesteDois</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B35">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
+          <t xml:space="preserve">Teste</t>
+        </is>
+      </c>
+      <c r="B35" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">TesteDois</t>
-        </is>
+          <t xml:space="preserve">0912</t>
+        </is>
+      </c>
+      <c t="n" r="D35">
+        <v>1</v>
       </c>
       <c t="n" r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H35">
@@ -1411,15 +1419,17 @@
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
-        </is>
-      </c>
-      <c r="B36" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste Teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">limitado</t>
+          <t xml:space="preserve">09121</t>
         </is>
       </c>
       <c t="n" r="D36">
@@ -1447,17 +1457,17 @@
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">expirado</t>
+          <t xml:space="preserve">Teste 2</t>
         </is>
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">acabou50</t>
+          <t xml:space="preserve">09122</t>
         </is>
       </c>
       <c t="n" r="E37">
@@ -1465,12 +1475,12 @@
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">04/12/2025 13:00:00</t>
+          <t xml:space="preserve">09/12/2025 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">05/12/2025 09:00:00</t>
+          <t xml:space="preserve">09/12/2025 13:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
@@ -1482,15 +1492,15 @@
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">cupom teste % 08/12/2025</t>
+          <t xml:space="preserve">cupom 09/12/25</t>
         </is>
       </c>
       <c r="B38" s="56">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">08122025</t>
+          <t xml:space="preserve">cupom101010</t>
         </is>
       </c>
       <c t="n" r="D38">
@@ -1501,24 +1511,24 @@
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
+          <t xml:space="preserve">cupom29929</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
@@ -1528,20 +1538,23 @@
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">0802200511</t>
-        </is>
+          <t xml:space="preserve">09082025</t>
+        </is>
+      </c>
+      <c t="n" r="D39">
+        <v>1</v>
       </c>
       <c t="n" r="E39">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">01/12/2025 04:00:00</t>
+          <t xml:space="preserve">09/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
+          <t xml:space="preserve">09/12/2025 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
@@ -1553,31 +1566,31 @@
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B40" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C40">
-        <is>
-          <t xml:space="preserve">0912</t>
-        </is>
+          <t xml:space="preserve">cupom data encerradda</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
+      </c>
+      <c r="C40" s="65">
+        <v>898989</v>
       </c>
       <c t="n" r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="n" r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">01/11/2025 02:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">09/12/2025 15:00:00</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
@@ -1589,21 +1602,16 @@
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Teste Teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B41">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">turma recorrente</t>
+        </is>
+      </c>
+      <c r="B41" s="56">
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">09121</t>
-        </is>
-      </c>
-      <c t="n" r="D41">
-        <v>1</v>
+          <t xml:space="preserve">teste09122025</t>
+        </is>
       </c>
       <c t="n" r="E41">
         <v>1</v>
@@ -1627,7 +1635,7 @@
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Teste 2</t>
+          <t xml:space="preserve">Teste 12/12-2</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
@@ -1637,20 +1645,23 @@
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">09122</t>
-        </is>
+          <t xml:space="preserve">Teste 12/12-2</t>
+        </is>
+      </c>
+      <c t="n" r="D42">
+        <v>1</v>
       </c>
       <c t="n" r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">09/12/2025 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">09/12/2025 13:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
@@ -1662,91 +1673,91 @@
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">cupom 09/12/25</t>
-        </is>
-      </c>
-      <c r="B43" s="56">
-        <v>0.11</v>
+          <t xml:space="preserve">caio expiração teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">cupom101010</t>
+          <t xml:space="preserve">caiocaiocaio</t>
         </is>
       </c>
       <c t="n" r="D43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="n" r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">12/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">09/12/2025 19:55:00</t>
+          <t xml:space="preserve">12/12/2025 11:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">caio101010</t>
+          <t xml:space="preserve">teste limite</t>
         </is>
       </c>
       <c t="inlineStr" r="B44">
         <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">testelimitete</t>
+        </is>
+      </c>
+      <c t="n" r="D44">
+        <v>1</v>
+      </c>
+      <c t="n" r="E44">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F44">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G44">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H44">
+        <is>
           <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C44">
-        <is>
-          <t xml:space="preserve">dinheiro</t>
-        </is>
-      </c>
-      <c t="n" r="D44">
-        <v>2</v>
-      </c>
-      <c t="n" r="E44">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="F44">
-        <is>
-          <t xml:space="preserve">09/12/2025 09:00:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G44">
-        <is>
-          <t xml:space="preserve">09/12/2025 12:20:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H44">
-        <is>
-          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">cupom29929</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B45">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">12/12 - 2</t>
+        </is>
+      </c>
+      <c r="B45" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">09082025</t>
+          <t xml:space="preserve">12/12 - 2</t>
         </is>
       </c>
       <c t="n" r="D45">
@@ -1757,12 +1768,12 @@
       </c>
       <c t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">09/12/2025 09:00:00</t>
+          <t xml:space="preserve">12/12/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">09/12/2025 10:00:00</t>
+          <t xml:space="preserve">12/12/2025 23:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
@@ -1774,31 +1785,31 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">cupom data encerradda</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B46">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c r="C46" s="65">
-        <v>898989</v>
+          <t xml:space="preserve">18/12</t>
+        </is>
+      </c>
+      <c r="B46" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">18/12</t>
+        </is>
       </c>
       <c t="n" r="D46">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c t="n" r="E46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">01/11/2025 02:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
@@ -1810,16 +1821,19 @@
     <row r="47">
       <c t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">turma recorrente</t>
+          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
         </is>
       </c>
       <c r="B47" s="56">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">teste09122025</t>
-        </is>
+          <t xml:space="preserve">caio18122025</t>
+        </is>
+      </c>
+      <c t="n" r="D47">
+        <v>1</v>
       </c>
       <c t="n" r="E47">
         <v>1</v>
@@ -1841,26 +1855,20 @@
       </c>
     </row>
     <row r="48">
-      <c t="inlineStr" r="A48">
-        <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B48">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C48">
-        <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
-        </is>
+      <c r="A48" s="56">
+        <v>1</v>
+      </c>
+      <c r="B48" s="56">
+        <v>1</v>
+      </c>
+      <c r="C48" s="56">
+        <v>1</v>
       </c>
       <c t="n" r="D48">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c t="n" r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F48">
         <is>
@@ -1881,21 +1889,18 @@
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">cupom 121225</t>
+          <t xml:space="preserve">18/12  cupom</t>
         </is>
       </c>
       <c t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">R$ 10.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">caio121225</t>
-        </is>
-      </c>
-      <c t="n" r="D49">
-        <v>1</v>
+          <t xml:space="preserve">18/12cupom</t>
+        </is>
       </c>
       <c t="n" r="E49">
         <v>1</v>
@@ -1919,30 +1924,31 @@
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">caio expiração teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B50">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">cupom 50%</t>
+        </is>
+      </c>
+      <c r="B50" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">caiocaiocaio</t>
-        </is>
+          <t xml:space="preserve">50%1812</t>
+        </is>
+      </c>
+      <c t="n" r="D50">
+        <v>1</v>
       </c>
       <c t="n" r="E50">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">12/12/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">12/12/2025 11:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
@@ -1954,7 +1960,7 @@
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">teste limite</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B51">
@@ -1962,13 +1968,8 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C51">
-        <is>
-          <t xml:space="preserve">testelimitete</t>
-        </is>
-      </c>
-      <c t="n" r="D51">
-        <v>1</v>
+      <c r="C51" s="65">
+        <v>969754</v>
       </c>
       <c t="n" r="E51">
         <v>0</v>
@@ -1985,14 +1986,14 @@
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
+          <t xml:space="preserve">teste metade</t>
         </is>
       </c>
       <c r="B52" s="56">
@@ -2000,23 +2001,20 @@
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
-        </is>
-      </c>
-      <c t="n" r="D52">
-        <v>1</v>
+          <t xml:space="preserve">0510</t>
+        </is>
       </c>
       <c t="n" r="E52">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c t="inlineStr" r="F52">
         <is>
-          <t xml:space="preserve">12/12/2025 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">12/12/2025 23:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
@@ -2028,7 +2026,7 @@
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">TesteLimite</t>
         </is>
       </c>
       <c r="B53" s="56">
@@ -2036,14 +2034,14 @@
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
       <c t="n" r="D53">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c t="n" r="E53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F53">
         <is>
@@ -2064,7 +2062,7 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
+          <t xml:space="preserve">Data expirada</t>
         </is>
       </c>
       <c r="B54" s="56">
@@ -2072,23 +2070,20 @@
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">caio18122025</t>
-        </is>
-      </c>
-      <c t="n" r="D54">
-        <v>1</v>
+          <t xml:space="preserve">0520</t>
+        </is>
       </c>
       <c t="n" r="E54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
@@ -2098,17 +2093,20 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="56">
-        <v>1</v>
-      </c>
-      <c r="B55" s="56">
-        <v>1</v>
-      </c>
-      <c r="C55" s="56">
-        <v>1</v>
-      </c>
-      <c t="n" r="D55">
-        <v>99</v>
+      <c t="inlineStr" r="A55">
+        <is>
+          <t xml:space="preserve">Valor Acima do minimo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">0530</t>
+        </is>
       </c>
       <c t="n" r="E55">
         <v>1</v>
@@ -2125,37 +2123,40 @@
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">18/12  cupom</t>
+          <t xml:space="preserve">teste cupom recorrente</t>
         </is>
       </c>
       <c t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">18/12cupom</t>
-        </is>
+          <t xml:space="preserve">cinco reais</t>
+        </is>
+      </c>
+      <c t="n" r="D56">
+        <v>1</v>
       </c>
       <c t="n" r="E56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 16:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
@@ -2167,22 +2168,22 @@
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">cupom 50%</t>
+          <t xml:space="preserve">teste06/01</t>
         </is>
       </c>
       <c r="B57" s="56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">50%1812</t>
+          <t xml:space="preserve">teste06/01</t>
         </is>
       </c>
       <c t="n" r="D57">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c t="n" r="E57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F57">
         <is>
@@ -2203,22 +2204,22 @@
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">trilha 18/12/25 xheflist c</t>
-        </is>
-      </c>
-      <c r="B58" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C58">
-        <is>
-          <t xml:space="preserve">50c1812</t>
-        </is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C58" s="65">
+        <v>1301</v>
       </c>
       <c t="n" r="D58">
         <v>1</v>
       </c>
       <c t="n" r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F58">
         <is>
@@ -2239,19 +2240,17 @@
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B59">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste2</t>
+        </is>
+      </c>
+      <c r="B59" s="56">
+        <v>0.5</v>
       </c>
       <c r="C59" s="65">
-        <v>969754</v>
+        <v>1302</v>
       </c>
       <c t="n" r="E59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F59">
         <is>
@@ -2265,26 +2264,28 @@
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">teste metade</t>
-        </is>
-      </c>
-      <c r="B60" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Desconto1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">0510</t>
+          <t xml:space="preserve">desc1</t>
         </is>
       </c>
       <c t="n" r="E60">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F60">
         <is>
@@ -2305,22 +2306,24 @@
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">TesteLimite</t>
-        </is>
-      </c>
-      <c r="B61" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Desconto2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
+          <t xml:space="preserve">desc2</t>
         </is>
       </c>
       <c t="n" r="D61">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c t="n" r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F61">
         <is>
@@ -2341,28 +2344,29 @@
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Data expirada</t>
+          <t xml:space="preserve">TesteLector14</t>
         </is>
       </c>
       <c r="B62" s="56">
         <v>0.5</v>
       </c>
-      <c t="inlineStr" r="C62">
-        <is>
-          <t xml:space="preserve">0520</t>
-        </is>
+      <c r="C62" s="65">
+        <v>12345678</v>
+      </c>
+      <c t="n" r="D62">
+        <v>1</v>
       </c>
       <c t="n" r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">05/01/2026 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">05/01/2026 14:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
@@ -2374,7 +2378,7 @@
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Valor Acima do minimo</t>
+          <t xml:space="preserve">Teste141414</t>
         </is>
       </c>
       <c t="inlineStr" r="B63">
@@ -2382,10 +2386,11 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C63">
-        <is>
-          <t xml:space="preserve">0530</t>
-        </is>
+      <c r="C63" s="65">
+        <v>123456789</v>
+      </c>
+      <c t="n" r="D63">
+        <v>1</v>
       </c>
       <c t="n" r="E63">
         <v>1</v>
@@ -2402,78 +2407,71 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">06/12/26 caio</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B64">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">15/01</t>
+        </is>
+      </c>
+      <c r="B64" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">0626 caio</t>
-        </is>
-      </c>
-      <c t="n" r="D64">
-        <v>1</v>
+          <t xml:space="preserve">15/01</t>
+        </is>
       </c>
       <c t="n" r="E64">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">06/01/2026 15:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t xml:space="preserve">06/01/2026 16:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">R$ 20.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">teste cupom recorrente</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B65">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">15/01</t>
+        </is>
+      </c>
+      <c r="B65" s="56">
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">cinco reais</t>
+          <t xml:space="preserve">15/01%</t>
         </is>
       </c>
       <c t="n" r="D65">
         <v>1</v>
       </c>
       <c t="n" r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t xml:space="preserve">06/01/2026 15:00:00</t>
+          <t xml:space="preserve">15/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t xml:space="preserve">06/01/2026 16:05:00</t>
+          <t xml:space="preserve">15/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
@@ -2485,22 +2483,20 @@
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">teste06/01</t>
+          <t xml:space="preserve">Teste 1515</t>
         </is>
       </c>
       <c r="B66" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C66">
-        <is>
-          <t xml:space="preserve">teste06/01</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="C66" s="65">
+        <v>1515</v>
       </c>
       <c t="n" r="D66">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F66">
         <is>
@@ -2521,7 +2517,7 @@
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">Teste 151515</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
@@ -2530,22 +2526,19 @@
         </is>
       </c>
       <c r="C67" s="65">
-        <v>1301</v>
-      </c>
-      <c t="n" r="D67">
-        <v>1</v>
+        <v>151515</v>
       </c>
       <c t="n" r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H67">
@@ -2557,14 +2550,16 @@
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">teste2</t>
-        </is>
-      </c>
-      <c r="B68" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 0115</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C68" s="65">
-        <v>1302</v>
+        <v>15151515</v>
       </c>
       <c t="n" r="E68">
         <v>1</v>
@@ -2588,30 +2583,31 @@
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Desconto1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B69">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste cupom 20/01</t>
+        </is>
+      </c>
+      <c r="B69" s="56">
+        <v>0.3</v>
       </c>
       <c t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">desc1</t>
-        </is>
+          <t xml:space="preserve">lc202601</t>
+        </is>
+      </c>
+      <c t="n" r="D69">
+        <v>20</v>
       </c>
       <c t="n" r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">20/01/2026 12:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">29/01/2026 18:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
@@ -2623,33 +2619,29 @@
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Desconto2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B70">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C70">
-        <is>
-          <t xml:space="preserve">desc2</t>
-        </is>
+          <t xml:space="preserve">Teste 2101</t>
+        </is>
+      </c>
+      <c r="B70" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C70" s="65">
+        <v>2101</v>
       </c>
       <c t="n" r="D70">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c t="n" r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G70">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 11:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H70">
@@ -2661,14 +2653,16 @@
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">TesteLector14</t>
-        </is>
-      </c>
-      <c r="B71" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C71" s="65">
-        <v>12345678</v>
+        <v>21012</v>
       </c>
       <c t="n" r="D71">
         <v>1</v>
@@ -2688,14 +2682,14 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Teste141414</t>
+          <t xml:space="preserve">Teste 100% 2101</t>
         </is>
       </c>
       <c t="inlineStr" r="B72">
@@ -2704,13 +2698,10 @@
         </is>
       </c>
       <c r="C72" s="65">
-        <v>123456789</v>
-      </c>
-      <c t="n" r="D72">
-        <v>1</v>
+        <v>2006</v>
       </c>
       <c t="n" r="E72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F72">
         <is>
@@ -2731,16 +2722,14 @@
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">15/01</t>
+          <t xml:space="preserve">Teste 21013</t>
         </is>
       </c>
       <c r="B73" s="56">
         <v>0.5</v>
       </c>
-      <c t="inlineStr" r="C73">
-        <is>
-          <t xml:space="preserve">15/01</t>
-        </is>
+      <c r="C73" s="65">
+        <v>21013</v>
       </c>
       <c t="n" r="E73">
         <v>0</v>
@@ -2764,31 +2753,31 @@
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">15/01</t>
+          <t xml:space="preserve">cupom teste 21/01</t>
         </is>
       </c>
       <c r="B74" s="56">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">15/01%</t>
+          <t xml:space="preserve">my20261</t>
         </is>
       </c>
       <c t="n" r="D74">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c t="n" r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">15/01/2026 12:00:00</t>
+          <t xml:space="preserve">21/01/2026 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">15/01/2026 14:00:00</t>
+          <t xml:space="preserve">21/01/2026 13:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
@@ -2800,17 +2789,19 @@
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">Teste 1515</t>
+          <t xml:space="preserve">cupom porcentagem</t>
         </is>
       </c>
       <c r="B75" s="56">
         <v>0.3</v>
       </c>
-      <c r="C75" s="65">
-        <v>1515</v>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">desconto30</t>
+        </is>
       </c>
       <c t="n" r="D75">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c t="n" r="E75">
         <v>1</v>
@@ -2834,28 +2825,31 @@
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Teste 151515</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B76">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C76" s="65">
-        <v>151515</v>
+          <t xml:space="preserve">cupom3030desconto</t>
+        </is>
+      </c>
+      <c r="B76" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">desconto30%</t>
+        </is>
+      </c>
+      <c t="n" r="D76">
+        <v>11</v>
       </c>
       <c t="n" r="E76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
@@ -2867,7 +2861,7 @@
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Teste 0115</t>
+          <t xml:space="preserve">Teste Metade 1</t>
         </is>
       </c>
       <c t="inlineStr" r="B77">
@@ -2876,10 +2870,10 @@
         </is>
       </c>
       <c r="C77" s="65">
-        <v>15151515</v>
+        <v>2201</v>
       </c>
       <c t="n" r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F77">
         <is>
@@ -2900,65 +2894,57 @@
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">teste cupom 20/01</t>
+          <t xml:space="preserve">Valor Minimo 2</t>
         </is>
       </c>
       <c r="B78" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C78">
-        <is>
-          <t xml:space="preserve">lc202601</t>
-        </is>
-      </c>
-      <c t="n" r="D78">
-        <v>20</v>
+        <v>0.01</v>
+      </c>
+      <c r="C78" s="65">
+        <v>2203</v>
       </c>
       <c t="n" r="E78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">20/01/2026 12:40:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G78">
         <is>
-          <t xml:space="preserve">29/01/2026 18:50:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 3.00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">Teste 2101</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B79" s="56">
         <v>0.5</v>
       </c>
       <c r="C79" s="65">
-        <v>2101</v>
-      </c>
-      <c t="n" r="D79">
-        <v>1</v>
+        <v>5656</v>
       </c>
       <c t="n" r="E79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">21/01/2026 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G79">
         <is>
-          <t xml:space="preserve">21/01/2026 11:35:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H79">
@@ -2968,57 +2954,54 @@
       </c>
     </row>
     <row r="80">
-      <c t="inlineStr" r="A80">
-        <is>
-          <t xml:space="preserve">Teste 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B80">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+      <c r="A80" s="65">
+        <v>2601</v>
+      </c>
+      <c r="B80" s="56">
+        <v>0.5</v>
       </c>
       <c r="C80" s="65">
-        <v>21012</v>
+        <v>2601</v>
       </c>
       <c t="n" r="D80">
         <v>1</v>
       </c>
       <c t="n" r="E80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G80">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">Teste 100% 2101</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B81">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">2601-1</t>
+        </is>
+      </c>
+      <c r="B81" s="56">
+        <v>0.5</v>
       </c>
       <c r="C81" s="65">
-        <v>2006</v>
+        <v>26011</v>
+      </c>
+      <c t="n" r="D81">
+        <v>1</v>
       </c>
       <c t="n" r="E81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F81">
         <is>
@@ -3039,26 +3022,26 @@
     <row r="82">
       <c t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">Teste 21013</t>
+          <t xml:space="preserve">2601-2</t>
         </is>
       </c>
       <c r="B82" s="56">
-        <v>0.5</v>
+        <v>260.12</v>
       </c>
       <c r="C82" s="65">
-        <v>21013</v>
+        <v>26012</v>
       </c>
       <c t="n" r="E82">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G82">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H82">
@@ -3068,33 +3051,28 @@
       </c>
     </row>
     <row r="83">
-      <c t="inlineStr" r="A83">
-        <is>
-          <t xml:space="preserve">cupom teste 21/01</t>
-        </is>
-      </c>
-      <c r="B83" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C83">
-        <is>
-          <t xml:space="preserve">my20261</t>
-        </is>
-      </c>
-      <c t="n" r="D83">
-        <v>11</v>
+      <c r="A83" s="65">
+        <v>26013</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C83" s="65">
+        <v>26013</v>
       </c>
       <c t="n" r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">21/01/2026 13:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">21/01/2026 13:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
@@ -3106,7 +3084,7 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">cupom porcentagem</t>
+          <t xml:space="preserve">cupom 27/01 checklist</t>
         </is>
       </c>
       <c r="B84" s="56">
@@ -3114,23 +3092,23 @@
       </c>
       <c t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">desconto30</t>
+          <t xml:space="preserve">semogoiac</t>
         </is>
       </c>
       <c t="n" r="D84">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c t="n" r="E84">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
@@ -3142,22 +3120,19 @@
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">cupom3030desconto</t>
+          <t xml:space="preserve">LECTOR10</t>
         </is>
       </c>
       <c r="B85" s="56">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">desconto30%</t>
-        </is>
-      </c>
-      <c t="n" r="D85">
-        <v>11</v>
+          <t xml:space="preserve">LECTOR10</t>
+        </is>
       </c>
       <c t="n" r="E85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F85">
         <is>
@@ -3178,50 +3153,58 @@
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Teste Metade 1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B86">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C86" s="65">
-        <v>2201</v>
+          <t xml:space="preserve">0602 Teste</t>
+        </is>
+      </c>
+      <c r="B86" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">0602</t>
+        </is>
+      </c>
+      <c t="n" r="D86">
+        <v>1</v>
       </c>
       <c t="n" r="E86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G86">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Valor Minimo 2</t>
+          <t xml:space="preserve">Teste 0602</t>
         </is>
       </c>
       <c r="B87" s="56">
-        <v>0.01</v>
-      </c>
-      <c r="C87" s="65">
-        <v>2203</v>
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">0602-1</t>
+        </is>
+      </c>
+      <c t="n" r="D87">
+        <v>1</v>
       </c>
       <c t="n" r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F87">
         <is>
@@ -3235,24 +3218,28 @@
       </c>
       <c t="inlineStr" r="H87">
         <is>
-          <t xml:space="preserve">R$ 3.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c r="B88" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C88" s="65">
-        <v>5656</v>
+          <t xml:space="preserve">0602-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">0602-3</t>
+        </is>
       </c>
       <c t="n" r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F88">
         <is>
@@ -3273,29 +3260,1083 @@
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
+          <t xml:space="preserve">cupomluiz</t>
+        </is>
+      </c>
+      <c r="B89" s="56">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">luiz100</t>
+        </is>
+      </c>
+      <c t="n" r="D89">
+        <v>100</v>
+      </c>
+      <c t="n" r="E89">
+        <v>11</v>
+      </c>
+      <c t="inlineStr" r="F89">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G89">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H89">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c t="inlineStr" r="A90">
+        <is>
           <t xml:space="preserve">teste</t>
         </is>
       </c>
-      <c r="B89" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C89" s="65">
-        <v>5757</v>
-      </c>
-      <c t="n" r="E89">
+      <c r="B90" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C90" s="65">
+        <v>1602</v>
+      </c>
+      <c t="n" r="D90">
+        <v>1</v>
+      </c>
+      <c t="n" r="E90">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F90">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G90">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H90">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c t="inlineStr" r="A91">
+        <is>
+          <t xml:space="preserve">Teste 1602</t>
+        </is>
+      </c>
+      <c r="B91" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C91" s="65">
+        <v>16021</v>
+      </c>
+      <c t="n" r="D91">
+        <v>1</v>
+      </c>
+      <c t="n" r="E91">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F91">
+        <is>
+          <t xml:space="preserve">16/02/2026 17:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G91">
+        <is>
+          <t xml:space="preserve">16/02/2026 23:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H91">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c t="inlineStr" r="A92">
+        <is>
+          <t xml:space="preserve">Teste 1602 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C92" s="65">
+        <v>16022</v>
+      </c>
+      <c t="n" r="E92">
+        <v>2</v>
+      </c>
+      <c t="inlineStr" r="F92">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G92">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H92">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c t="inlineStr" r="A93">
+        <is>
+          <t xml:space="preserve">teste cupom</t>
+        </is>
+      </c>
+      <c r="B93" s="56">
+        <v>0.11</v>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">codigo10teste</t>
+        </is>
+      </c>
+      <c t="n" r="E93">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F93">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G93">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H93">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c t="inlineStr" r="A94">
+        <is>
+          <t xml:space="preserve">Cupom Cypress</t>
+        </is>
+      </c>
+      <c r="B94" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C94" s="65">
+        <v>808182</v>
+      </c>
+      <c t="n" r="D94">
+        <v>80</v>
+      </c>
+      <c t="n" r="E94">
+        <v>2</v>
+      </c>
+      <c t="inlineStr" r="F94">
+        <is>
+          <t xml:space="preserve">01/01/2026 10:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G94">
+        <is>
+          <t xml:space="preserve">05/12/2026 18:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H94">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c t="inlineStr" r="A95">
+        <is>
+          <t xml:space="preserve">Valor Minimo 3</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C95" s="65">
+        <v>1901</v>
+      </c>
+      <c t="n" r="E95">
         <v>0</v>
       </c>
-      <c t="inlineStr" r="F89">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G89">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H89">
+      <c t="inlineStr" r="F95">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G95">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H95">
+        <is>
+          <t xml:space="preserve">R$ 100.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c t="inlineStr" r="A96">
+        <is>
+          <t xml:space="preserve">cupom10trilha</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">cupom10trilha</t>
+        </is>
+      </c>
+      <c t="n" r="D96">
+        <v>5</v>
+      </c>
+      <c t="n" r="E96">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F96">
+        <is>
+          <t xml:space="preserve">23/02/2026 17:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G96">
+        <is>
+          <t xml:space="preserve">23/02/2026 17:55:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H96">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c t="inlineStr" r="A97">
+        <is>
+          <t xml:space="preserve">Teste100</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C97" s="65">
+        <v>99</v>
+      </c>
+      <c t="n" r="E97">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F97">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G97">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H97">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c t="inlineStr" r="A98">
+        <is>
+          <t xml:space="preserve">Teste 200</t>
+        </is>
+      </c>
+      <c r="B98" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C98" s="65">
+        <v>88</v>
+      </c>
+      <c t="n" r="E98">
+        <v>3</v>
+      </c>
+      <c t="inlineStr" r="F98">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G98">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H98">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c t="inlineStr" r="A99">
+        <is>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c r="B99" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C99" s="65">
+        <v>77</v>
+      </c>
+      <c t="n" r="E99">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F99">
+        <is>
+          <t xml:space="preserve">24/02/2026 10:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G99">
+        <is>
+          <t xml:space="preserve">24/02/2026 10:10:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H99">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c t="inlineStr" r="A100">
+        <is>
+          <t xml:space="preserve">teste 3</t>
+        </is>
+      </c>
+      <c r="B100" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C100" s="65">
+        <v>55</v>
+      </c>
+      <c t="n" r="E100">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F100">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G100">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H100">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c t="inlineStr" r="A101">
+        <is>
+          <t xml:space="preserve">teste 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C101" s="65">
+        <v>44</v>
+      </c>
+      <c t="n" r="D101">
+        <v>1</v>
+      </c>
+      <c t="n" r="E101">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F101">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G101">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H101">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c t="inlineStr" r="A102">
+        <is>
+          <t xml:space="preserve">Vencido</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C102" s="65">
+        <v>202020</v>
+      </c>
+      <c t="n" r="E102">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F102">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G102">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H102">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c t="inlineStr" r="A103">
+        <is>
+          <t xml:space="preserve">Real 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C103" s="65">
+        <v>303030</v>
+      </c>
+      <c t="n" r="E103">
+        <v>2</v>
+      </c>
+      <c t="inlineStr" r="F103">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G103">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H103">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c t="inlineStr" r="A104">
+        <is>
+          <t xml:space="preserve">Real 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C104" s="65">
+        <v>404040</v>
+      </c>
+      <c t="n" r="D104">
+        <v>1</v>
+      </c>
+      <c t="n" r="E104">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F104">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G104">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H104">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c t="inlineStr" r="A105">
+        <is>
+          <t xml:space="preserve">Porcentagem</t>
+        </is>
+      </c>
+      <c r="B105" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C105" s="65">
+        <v>707070</v>
+      </c>
+      <c t="n" r="E105">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F105">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G105">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H105">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c t="inlineStr" r="A106">
+        <is>
+          <t xml:space="preserve">Valor minimo</t>
+        </is>
+      </c>
+      <c r="B106" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C106" s="65">
+        <v>909090</v>
+      </c>
+      <c t="n" r="E106">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F106">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G106">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H106">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c t="inlineStr" r="A107">
+        <is>
+          <t xml:space="preserve">teste ext</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C107" s="65">
+        <v>959595</v>
+      </c>
+      <c t="n" r="E107">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F107">
+        <is>
+          <t xml:space="preserve">26/02/2026 09:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G107">
+        <is>
+          <t xml:space="preserve">26/02/2026 09:20:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H107">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c t="inlineStr" r="A108">
+        <is>
+          <t xml:space="preserve">teste 03</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">0303</t>
+        </is>
+      </c>
+      <c t="n" r="D108">
+        <v>1</v>
+      </c>
+      <c t="n" r="E108">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F108">
+        <is>
+          <t xml:space="preserve">03/03/2026 13:40:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G108">
+        <is>
+          <t xml:space="preserve">03/03/2026 14:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H108">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c t="inlineStr" r="A109">
+        <is>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c r="B109" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C109" s="65">
+        <v>330</v>
+      </c>
+      <c t="n" r="E109">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F109">
+        <is>
+          <t xml:space="preserve">03/03/2026 13:35:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G109">
+        <is>
+          <t xml:space="preserve">03/03/2026 13:40:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H109">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c t="inlineStr" r="A110">
+        <is>
+          <t xml:space="preserve">teste trilha</t>
+        </is>
+      </c>
+      <c r="B110" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C110" s="65">
+        <v>61615</v>
+      </c>
+      <c t="n" r="E110">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F110">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G110">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H110">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c t="inlineStr" r="A111">
+        <is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B111" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C111" s="65">
+        <v>61617</v>
+      </c>
+      <c t="n" r="E111">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F111">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G111">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H111">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c t="inlineStr" r="A112">
+        <is>
+          <t xml:space="preserve">cupom teste 12</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C112" s="65">
+        <v>1203</v>
+      </c>
+      <c t="n" r="E112">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F112">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G112">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H112">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c t="inlineStr" r="A113">
+        <is>
+          <t xml:space="preserve">cupom teste 13</t>
+        </is>
+      </c>
+      <c r="B113" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C113" s="65">
+        <v>1204</v>
+      </c>
+      <c t="n" r="D113">
+        <v>1</v>
+      </c>
+      <c t="n" r="E113">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F113">
+        <is>
+          <t xml:space="preserve">12/03/2026 08:45:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G113">
+        <is>
+          <t xml:space="preserve">12/03/2026 09:30:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H113">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c t="inlineStr" r="A114">
+        <is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B114" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C114" s="65">
+        <v>1205</v>
+      </c>
+      <c t="n" r="E114">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F114">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G114">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H114">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c t="inlineStr" r="A115">
+        <is>
+          <t xml:space="preserve">100% Teste</t>
+        </is>
+      </c>
+      <c r="B115" s="56">
+        <v>1</v>
+      </c>
+      <c r="C115" s="65">
+        <v>13033</v>
+      </c>
+      <c t="n" r="E115">
+        <v>2</v>
+      </c>
+      <c t="inlineStr" r="F115">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G115">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H115">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c t="inlineStr" r="A116">
+        <is>
+          <t xml:space="preserve">Teste 1703</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C116" s="65">
+        <v>17031</v>
+      </c>
+      <c t="n" r="D116">
+        <v>1</v>
+      </c>
+      <c t="n" r="E116">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F116">
+        <is>
+          <t xml:space="preserve">17/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G116">
+        <is>
+          <t xml:space="preserve">18/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H116">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c t="inlineStr" r="A117">
+        <is>
+          <t xml:space="preserve">Teste 2 1703 expirado</t>
+        </is>
+      </c>
+      <c r="B117" s="56">
+        <v>5</v>
+      </c>
+      <c r="C117" s="65">
+        <v>17032</v>
+      </c>
+      <c t="n" r="E117">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F117">
+        <is>
+          <t xml:space="preserve">17/03/2026 00:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G117">
+        <is>
+          <t xml:space="preserve">17/03/2026 11:00:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H117">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c t="inlineStr" r="A118">
+        <is>
+          <t xml:space="preserve">Teste3 1703</t>
+        </is>
+      </c>
+      <c r="B118" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C118" s="65">
+        <v>17033</v>
+      </c>
+      <c t="n" r="E118">
+        <v>4</v>
+      </c>
+      <c t="inlineStr" r="F118">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G118">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H118">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c t="inlineStr" r="A119">
+        <is>
+          <t xml:space="preserve">ValorAcimaDoMinimo2</t>
+        </is>
+      </c>
+      <c r="B119" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C119" s="65">
+        <v>919293</v>
+      </c>
+      <c t="n" r="E119">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F119">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G119">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H119">
+        <is>
+          <t xml:space="preserve">R$ 50.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65">
+        <v>777</v>
+      </c>
+      <c t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C120" s="65">
+        <v>111225</v>
+      </c>
+      <c t="n" r="E120">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F120">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G120">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H120">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c t="inlineStr" r="A121">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+      <c r="B121" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C121" s="65">
+        <v>2025</v>
+      </c>
+      <c t="n" r="E121">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F121">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G121">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H121">
         <is>
           <t xml:space="preserve">-</t>
         </is>

--- a/cypress/downloads/Plataforma externa Volta Redonda.xlsx
+++ b/cypress/downloads/Plataforma externa Volta Redonda.xlsx
@@ -269,174 +269,171 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">DIA23JUNHO</t>
+          <t xml:space="preserve">Teste2306</t>
         </is>
       </c>
       <c r="B3" s="56">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">DIA23JUNHO</t>
+          <t xml:space="preserve">teste2306</t>
         </is>
       </c>
       <c t="n" r="D3">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c t="n" r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">23/06/2025 08:00:00</t>
+          <t xml:space="preserve">23/06/2025 15:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">30/06/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">Teste2306</t>
+          <t xml:space="preserve">dia17</t>
         </is>
       </c>
       <c r="B4" s="56">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">teste2306</t>
+          <t xml:space="preserve">dia17</t>
         </is>
       </c>
       <c t="n" r="D4">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c t="n" r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">23/06/2025 15:25:00</t>
+          <t xml:space="preserve">17/07/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">17/07/2025 19:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">dia17</t>
+          <t xml:space="preserve">teste08/08</t>
         </is>
       </c>
       <c r="B5" s="56">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">dia17</t>
+          <t xml:space="preserve">teste08/08</t>
         </is>
       </c>
       <c t="n" r="D5">
         <v>100</v>
       </c>
       <c t="n" r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">17/07/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">17/07/2025 19:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 10.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">teste08/08</t>
-        </is>
-      </c>
-      <c r="B6" s="56">
-        <v>0.1</v>
+          <t xml:space="preserve">testecupom</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B6">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">teste08/08</t>
-        </is>
-      </c>
-      <c t="n" r="D6">
-        <v>100</v>
+          <t xml:space="preserve">testecupom</t>
+        </is>
       </c>
       <c t="n" r="E6">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">20/08/2025 09:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">22/08/2025 11:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">testecupom</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B7">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
+          <t xml:space="preserve">testecupom21/08</t>
+        </is>
+      </c>
+      <c r="B7" s="56">
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">testecupom</t>
+          <t xml:space="preserve">testecupom21/08</t>
         </is>
       </c>
       <c t="n" r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t xml:space="preserve">20/08/2025 09:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">22/08/2025 11:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
@@ -448,7 +445,7 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">testecupom21/08</t>
+          <t xml:space="preserve">Cupom7</t>
         </is>
       </c>
       <c r="B8" s="56">
@@ -456,8 +453,11 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">testecupom21/08</t>
-        </is>
+          <t xml:space="preserve">0712</t>
+        </is>
+      </c>
+      <c t="n" r="D8">
+        <v>8</v>
       </c>
       <c t="n" r="E8">
         <v>3</v>
@@ -481,22 +481,17 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">Cupom7</t>
+          <t xml:space="preserve">CUPOM TESTE</t>
         </is>
       </c>
       <c r="B9" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C9">
-        <is>
-          <t xml:space="preserve">0712</t>
-        </is>
-      </c>
-      <c t="n" r="D9">
-        <v>8</v>
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="65">
+        <v>1010</v>
       </c>
       <c t="n" r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
@@ -517,26 +512,33 @@
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">CUPOM TESTE</t>
-        </is>
-      </c>
-      <c r="B10" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C10" s="65">
-        <v>1010</v>
+          <t xml:space="preserve">Testecupom</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B10">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C10">
+        <is>
+          <t xml:space="preserve">Testecupom</t>
+        </is>
+      </c>
+      <c t="n" r="D10">
+        <v>50</v>
       </c>
       <c t="n" r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23/09/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/09/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
@@ -548,33 +550,28 @@
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">Testecupom</t>
+          <t xml:space="preserve">TESTE</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C11">
-        <is>
-          <t xml:space="preserve">Testecupom</t>
-        </is>
-      </c>
-      <c t="n" r="D11">
-        <v>50</v>
+          <t xml:space="preserve">R$ 60.00</t>
+        </is>
+      </c>
+      <c r="C11" s="65">
+        <v>606060</v>
       </c>
       <c t="n" r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">23/09/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">26/09/2025 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
@@ -589,16 +586,14 @@
           <t xml:space="preserve">TESTE</t>
         </is>
       </c>
-      <c t="inlineStr" r="B12">
-        <is>
-          <t xml:space="preserve">R$ 60.00</t>
-        </is>
+      <c r="B12" s="56">
+        <v>0.5</v>
       </c>
       <c r="C12" s="65">
-        <v>606060</v>
+        <v>505050</v>
       </c>
       <c t="n" r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
@@ -619,17 +614,17 @@
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">TESTE</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B13" s="56">
         <v>0.5</v>
       </c>
       <c r="C13" s="65">
-        <v>505050</v>
+        <v>4040</v>
       </c>
       <c t="n" r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -650,17 +645,24 @@
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c r="B14" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C14" s="65">
-        <v>4040</v>
+          <t xml:space="preserve">teste2609</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">teste2609</t>
+        </is>
+      </c>
+      <c t="n" r="D14">
+        <v>100</v>
       </c>
       <c t="n" r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F14">
         <is>
@@ -681,7 +683,7 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">teste2609</t>
+          <t xml:space="preserve">testecupom10/10</t>
         </is>
       </c>
       <c t="inlineStr" r="B15">
@@ -691,7 +693,7 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">teste2609</t>
+          <t xml:space="preserve">testecupom10/10</t>
         </is>
       </c>
       <c t="n" r="D15">
@@ -702,12 +704,12 @@
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">10/10/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">11/10/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
@@ -719,17 +721,15 @@
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">testecupom10/10</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B16">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
+          <t xml:space="preserve">cupom14/10</t>
+        </is>
+      </c>
+      <c r="B16" s="56">
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">testecupom10/10</t>
+          <t xml:space="preserve">cupom14/10</t>
         </is>
       </c>
       <c t="n" r="D16">
@@ -740,12 +740,12 @@
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">10/10/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">11/10/2025 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
@@ -757,22 +757,17 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">cupom14/10</t>
+          <t xml:space="preserve">Cupom50</t>
         </is>
       </c>
       <c r="B17" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C17">
-        <is>
-          <t xml:space="preserve">cupom14/10</t>
-        </is>
-      </c>
-      <c t="n" r="D17">
-        <v>100</v>
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="65">
+        <v>3110</v>
       </c>
       <c t="n" r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F17">
         <is>
@@ -793,48 +788,53 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">Cupom50</t>
+          <t xml:space="preserve">Teste12/11</t>
         </is>
       </c>
       <c r="B18" s="56">
         <v>0.5</v>
       </c>
       <c r="C18" s="65">
-        <v>3110</v>
+        <v>105</v>
+      </c>
+      <c t="n" r="D18">
+        <v>10</v>
       </c>
       <c t="n" r="E18">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">Teste12/11</t>
-        </is>
-      </c>
-      <c r="B19" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">TESTE12/11</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C19" s="65">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c t="n" r="D19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c t="n" r="E19">
         <v>1</v>
@@ -858,62 +858,60 @@
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B20">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">cupom502</t>
+        </is>
+      </c>
+      <c r="B20" s="56">
+        <v>0.5</v>
       </c>
       <c r="C20" s="65">
-        <v>201</v>
-      </c>
-      <c t="n" r="D20">
-        <v>1</v>
+        <v>5486</v>
       </c>
       <c t="n" r="E20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">01/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">cupom502</t>
+          <t xml:space="preserve">TESTE12/11</t>
         </is>
       </c>
       <c r="B21" s="56">
         <v>0.5</v>
       </c>
       <c r="C21" s="65">
-        <v>5486</v>
+        <v>47992458811</v>
+      </c>
+      <c t="n" r="D21">
+        <v>100</v>
       </c>
       <c t="n" r="E21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/01/2026 07:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
@@ -925,29 +923,29 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
+          <t xml:space="preserve">Teste</t>
         </is>
       </c>
       <c r="B22" s="56">
         <v>0.5</v>
       </c>
       <c r="C22" s="65">
-        <v>47992458811</v>
+        <v>1617</v>
       </c>
       <c t="n" r="D22">
         <v>100</v>
       </c>
       <c t="n" r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">12/11/2025 16:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">03/01/2026 07:35:00</t>
+          <t xml:space="preserve">12/11/2025 16:20:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
@@ -959,14 +957,16 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B23" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Testeeeee</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
       </c>
       <c r="C23" s="65">
-        <v>1617</v>
+        <v>2222</v>
       </c>
       <c t="n" r="D23">
         <v>100</v>
@@ -976,12 +976,12 @@
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">12/11/2025 16:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">12/11/2025 16:20:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
@@ -993,22 +993,19 @@
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">Testeeeee</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B24">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c r="C24" s="65">
-        <v>2222</v>
-      </c>
-      <c t="n" r="D24">
-        <v>100</v>
+          <t xml:space="preserve">Teste17/11</t>
+        </is>
+      </c>
+      <c r="B24" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Teste17/11</t>
+        </is>
       </c>
       <c t="n" r="E24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
@@ -1029,33 +1026,34 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">Teste17/11</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B25" s="56">
         <v>0.5</v>
       </c>
-      <c t="inlineStr" r="C25">
-        <is>
-          <t xml:space="preserve">Teste17/11</t>
-        </is>
+      <c r="C25" s="65">
+        <v>5050</v>
+      </c>
+      <c t="n" r="D25">
+        <v>10</v>
       </c>
       <c t="n" r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/11/2025 14:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
@@ -1065,47 +1063,49 @@
           <t xml:space="preserve">teste</t>
         </is>
       </c>
-      <c r="B26" s="56">
-        <v>0.5</v>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c r="C26" s="65">
-        <v>5050</v>
+        <v>123</v>
       </c>
       <c t="n" r="D26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c t="n" r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">21/11/2025 14:55:00</t>
+          <t xml:space="preserve">18/11/2025 13:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
         <is>
-          <t xml:space="preserve">21/11/2025 15:55:00</t>
+          <t xml:space="preserve">19/11/2025 14:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B27">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c r="C27" s="65">
-        <v>123</v>
+          <t xml:space="preserve">testes 2111</t>
+        </is>
+      </c>
+      <c r="B27" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">date123</t>
+        </is>
       </c>
       <c t="n" r="D27">
         <v>5</v>
@@ -1115,12 +1115,12 @@
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">18/11/2025 13:45:00</t>
+          <t xml:space="preserve">18/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">19/11/2025 14:50:00</t>
+          <t xml:space="preserve">19/11/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
@@ -1132,95 +1132,95 @@
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">testes 2111</t>
-        </is>
-      </c>
-      <c r="B28" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 04/12-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">date123</t>
+          <t xml:space="preserve">Teste 04/12-1</t>
         </is>
       </c>
       <c t="n" r="D28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">18/11/2025 15:55:00</t>
+          <t xml:space="preserve">04/12/2025 10:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">19/11/2025 19:55:00</t>
+          <t xml:space="preserve">04/12/2025 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
+          <t xml:space="preserve">TesteDois</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
-        </is>
-      </c>
-      <c t="n" r="D29">
-        <v>1</v>
+          <t xml:space="preserve">TesteDois</t>
+        </is>
       </c>
       <c t="n" r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">04/12/2025 10:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">04/12/2025 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">TesteDois</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B30">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
+          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
+        </is>
+      </c>
+      <c r="B30" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">TesteDois</t>
-        </is>
+          <t xml:space="preserve">limitado</t>
+        </is>
+      </c>
+      <c t="n" r="D30">
+        <v>1</v>
       </c>
       <c t="n" r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F30">
         <is>
@@ -1241,31 +1241,30 @@
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
-        </is>
-      </c>
-      <c r="B31" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">limitado</t>
-        </is>
-      </c>
-      <c t="n" r="D31">
-        <v>1</v>
+          <t xml:space="preserve">acabou50</t>
+        </is>
       </c>
       <c t="n" r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">04/12/2025 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
@@ -1277,30 +1276,31 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">expirado</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B32">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">cupom teste % 08/12/2025</t>
+        </is>
+      </c>
+      <c r="B32" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">acabou50</t>
-        </is>
+          <t xml:space="preserve">08122025</t>
+        </is>
+      </c>
+      <c t="n" r="D32">
+        <v>1</v>
       </c>
       <c t="n" r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">04/12/2025 13:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">05/12/2025 09:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
@@ -1312,31 +1312,30 @@
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">cupom teste % 08/12/2025</t>
-        </is>
-      </c>
-      <c r="B33" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">08122025</t>
-        </is>
-      </c>
-      <c t="n" r="D33">
-        <v>1</v>
+          <t xml:space="preserve">0802200511</t>
+        </is>
       </c>
       <c t="n" r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/12/2025 04:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
@@ -1348,30 +1347,31 @@
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B34">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">Teste</t>
+        </is>
+      </c>
+      <c r="B34" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">0802200511</t>
-        </is>
+          <t xml:space="preserve">0912</t>
+        </is>
+      </c>
+      <c t="n" r="D34">
+        <v>1</v>
       </c>
       <c t="n" r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">01/12/2025 04:00:00</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
+          <t xml:space="preserve">09/12/2025 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
@@ -1383,15 +1383,17 @@
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B35" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste Teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">0912</t>
+          <t xml:space="preserve">09121</t>
         </is>
       </c>
       <c t="n" r="D35">
@@ -1402,12 +1404,12 @@
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
         <is>
-          <t xml:space="preserve">09/12/2025 15:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H35">
@@ -1419,7 +1421,7 @@
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">Teste Teste</t>
+          <t xml:space="preserve">Teste 2</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
@@ -1429,23 +1431,20 @@
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">09121</t>
-        </is>
-      </c>
-      <c t="n" r="D36">
-        <v>1</v>
+          <t xml:space="preserve">09122</t>
+        </is>
       </c>
       <c t="n" r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 13:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
@@ -1457,78 +1456,81 @@
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">Teste 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B37">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">cupom 09/12/25</t>
+        </is>
+      </c>
+      <c r="B37" s="56">
+        <v>0.11</v>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">09122</t>
-        </is>
+          <t xml:space="preserve">cupom101010</t>
+        </is>
+      </c>
+      <c t="n" r="D37">
+        <v>1</v>
       </c>
       <c t="n" r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">09/12/2025 12:00:00</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">09/12/2025 13:10:00</t>
+          <t xml:space="preserve">09/12/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">cupom 09/12/25</t>
-        </is>
-      </c>
-      <c r="B38" s="56">
-        <v>0.11</v>
+          <t xml:space="preserve">cupom29929</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">cupom101010</t>
+          <t xml:space="preserve">09082025</t>
         </is>
       </c>
       <c t="n" r="D38">
         <v>1</v>
       </c>
       <c t="n" r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">09/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">09/12/2025 19:55:00</t>
+          <t xml:space="preserve">09/12/2025 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">cupom29929</t>
+          <t xml:space="preserve">cupom data encerradda</t>
         </is>
       </c>
       <c t="inlineStr" r="B39">
@@ -1536,25 +1538,23 @@
           <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C39">
-        <is>
-          <t xml:space="preserve">09082025</t>
-        </is>
+      <c r="C39" s="65">
+        <v>898989</v>
       </c>
       <c t="n" r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="n" r="E39">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">09/12/2025 09:00:00</t>
+          <t xml:space="preserve">01/11/2025 02:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">09/12/2025 10:00:00</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
@@ -1566,31 +1566,28 @@
     <row r="40">
       <c t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">cupom data encerradda</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B40">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c r="C40" s="65">
-        <v>898989</v>
-      </c>
-      <c t="n" r="D40">
-        <v>2</v>
+          <t xml:space="preserve">turma recorrente</t>
+        </is>
+      </c>
+      <c r="B40" s="56">
+        <v>0.1</v>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">teste09122025</t>
+        </is>
       </c>
       <c t="n" r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">01/11/2025 02:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
@@ -1602,16 +1599,21 @@
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">turma recorrente</t>
-        </is>
-      </c>
-      <c r="B41" s="56">
-        <v>0.1</v>
+          <t xml:space="preserve">Teste 12/12-2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">teste09122025</t>
-        </is>
+          <t xml:space="preserve">Teste 12/12-2</t>
+        </is>
+      </c>
+      <c t="n" r="D41">
+        <v>1</v>
       </c>
       <c t="n" r="E41">
         <v>1</v>
@@ -1635,33 +1637,33 @@
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
+          <t xml:space="preserve">caio expiração teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
+          <t xml:space="preserve">caiocaiocaio</t>
         </is>
       </c>
       <c t="n" r="D42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="n" r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 11:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
@@ -1673,55 +1675,53 @@
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">caio expiração teste</t>
+          <t xml:space="preserve">teste limite</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">caiocaiocaio</t>
+          <t xml:space="preserve">testelimitete</t>
         </is>
       </c>
       <c t="n" r="D43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E43">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">12/12/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">12/12/2025 11:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">teste limite</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B44">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">12/12 - 2</t>
+        </is>
+      </c>
+      <c r="B44" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">testelimitete</t>
+          <t xml:space="preserve">12/12 - 2</t>
         </is>
       </c>
       <c t="n" r="D44">
@@ -1732,24 +1732,24 @@
       </c>
       <c t="inlineStr" r="F44">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 23:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
+          <t xml:space="preserve">18/12</t>
         </is>
       </c>
       <c r="B45" s="56">
@@ -1757,23 +1757,23 @@
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
+          <t xml:space="preserve">18/12</t>
         </is>
       </c>
       <c t="n" r="D45">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c t="n" r="E45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">12/12/2025 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">12/12/2025 23:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
@@ -1785,7 +1785,7 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
         </is>
       </c>
       <c r="B46" s="56">
@@ -1793,50 +1793,46 @@
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">caio18122025</t>
         </is>
       </c>
       <c t="n" r="D46">
+        <v>1</v>
+      </c>
+      <c t="n" r="E46">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F46">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G46">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H46">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56">
+        <v>1</v>
+      </c>
+      <c r="B47" s="56">
+        <v>1</v>
+      </c>
+      <c r="C47" s="56">
+        <v>1</v>
+      </c>
+      <c t="n" r="D47">
         <v>99</v>
       </c>
-      <c t="n" r="E46">
-        <v>3</v>
-      </c>
-      <c t="inlineStr" r="F46">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G46">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H46">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c t="inlineStr" r="A47">
-        <is>
-          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
-        </is>
-      </c>
-      <c r="B47" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C47">
-        <is>
-          <t xml:space="preserve">caio18122025</t>
-        </is>
-      </c>
-      <c t="n" r="D47">
-        <v>1</v>
-      </c>
       <c t="n" r="E47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F47">
         <is>
@@ -1855,20 +1851,23 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="56">
-        <v>1</v>
-      </c>
-      <c r="B48" s="56">
-        <v>1</v>
-      </c>
-      <c r="C48" s="56">
-        <v>1</v>
-      </c>
-      <c t="n" r="D48">
-        <v>99</v>
+      <c t="inlineStr" r="A48">
+        <is>
+          <t xml:space="preserve">18/12  cupom</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">18/12cupom</t>
+        </is>
       </c>
       <c t="n" r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F48">
         <is>
@@ -1889,21 +1888,22 @@
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">18/12  cupom</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B49">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
+          <t xml:space="preserve">cupom 50%</t>
+        </is>
+      </c>
+      <c r="B49" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">18/12cupom</t>
-        </is>
+          <t xml:space="preserve">50%1812</t>
+        </is>
+      </c>
+      <c t="n" r="D49">
+        <v>1</v>
       </c>
       <c t="n" r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F49">
         <is>
@@ -1924,19 +1924,16 @@
     <row r="50">
       <c t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">cupom 50%</t>
-        </is>
-      </c>
-      <c r="B50" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C50">
-        <is>
-          <t xml:space="preserve">50%1812</t>
-        </is>
-      </c>
-      <c t="n" r="D50">
-        <v>1</v>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C50" s="65">
+        <v>969754</v>
       </c>
       <c t="n" r="E50">
         <v>0</v>
@@ -1953,26 +1950,26 @@
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B51">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C51" s="65">
-        <v>969754</v>
+          <t xml:space="preserve">teste metade</t>
+        </is>
+      </c>
+      <c r="B51" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">0510</t>
+        </is>
       </c>
       <c t="n" r="E51">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c t="inlineStr" r="F51">
         <is>
@@ -1986,14 +1983,14 @@
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">teste metade</t>
+          <t xml:space="preserve">TesteLimite</t>
         </is>
       </c>
       <c r="B52" s="56">
@@ -2001,11 +1998,14 @@
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">0510</t>
-        </is>
+          <t xml:space="preserve">05/01/2026</t>
+        </is>
+      </c>
+      <c t="n" r="D52">
+        <v>1</v>
       </c>
       <c t="n" r="E52">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F52">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">TesteLimite</t>
+          <t xml:space="preserve">Data expirada</t>
         </is>
       </c>
       <c r="B53" s="56">
@@ -2034,23 +2034,20 @@
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
-        </is>
-      </c>
-      <c t="n" r="D53">
-        <v>1</v>
+          <t xml:space="preserve">0520</t>
+        </is>
       </c>
       <c t="n" r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F53">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
@@ -2062,101 +2059,104 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Data expirada</t>
-        </is>
-      </c>
-      <c r="B54" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Valor Acima do minimo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">0520</t>
+          <t xml:space="preserve">0530</t>
         </is>
       </c>
       <c t="n" r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">05/01/2026 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">05/01/2026 14:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">Valor Acima do minimo</t>
+          <t xml:space="preserve">teste cupom recorrente</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">0530</t>
-        </is>
+          <t xml:space="preserve">cinco reais</t>
+        </is>
+      </c>
+      <c t="n" r="D55">
+        <v>1</v>
       </c>
       <c t="n" r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 16:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">teste cupom recorrente</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B56">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">teste06/01</t>
+        </is>
+      </c>
+      <c r="B56" s="56">
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">cinco reais</t>
+          <t xml:space="preserve">teste06/01</t>
         </is>
       </c>
       <c t="n" r="D56">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c t="n" r="E56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">06/01/2026 15:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">06/01/2026 16:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
@@ -2168,22 +2168,22 @@
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">teste06/01</t>
-        </is>
-      </c>
-      <c r="B57" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C57">
-        <is>
-          <t xml:space="preserve">teste06/01</t>
-        </is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C57" s="65">
+        <v>1301</v>
       </c>
       <c t="n" r="D57">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F57">
         <is>
@@ -2204,19 +2204,14 @@
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B58">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste2</t>
+        </is>
+      </c>
+      <c r="B58" s="56">
+        <v>0.5</v>
       </c>
       <c r="C58" s="65">
-        <v>1301</v>
-      </c>
-      <c t="n" r="D58">
-        <v>1</v>
+        <v>1302</v>
       </c>
       <c t="n" r="E58">
         <v>1</v>
@@ -2240,17 +2235,21 @@
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">teste2</t>
-        </is>
-      </c>
-      <c r="B59" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C59" s="65">
-        <v>1302</v>
+          <t xml:space="preserve">Desconto1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">desc1</t>
+        </is>
       </c>
       <c t="n" r="E59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F59">
         <is>
@@ -2271,18 +2270,21 @@
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Desconto1</t>
+          <t xml:space="preserve">Desconto2</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">desc1</t>
-        </is>
+          <t xml:space="preserve">desc2</t>
+        </is>
+      </c>
+      <c t="n" r="D60">
+        <v>10</v>
       </c>
       <c t="n" r="E60">
         <v>0</v>
@@ -2306,24 +2308,20 @@
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">Desconto2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B61">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C61">
-        <is>
-          <t xml:space="preserve">desc2</t>
-        </is>
+          <t xml:space="preserve">TesteLector14</t>
+        </is>
+      </c>
+      <c r="B61" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C61" s="65">
+        <v>12345678</v>
       </c>
       <c t="n" r="D61">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c t="n" r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F61">
         <is>
@@ -2344,14 +2342,16 @@
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">TesteLector14</t>
-        </is>
-      </c>
-      <c r="B62" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste141414</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C62" s="65">
-        <v>12345678</v>
+        <v>123456789</v>
       </c>
       <c t="n" r="D62">
         <v>1</v>
@@ -2378,22 +2378,19 @@
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">Teste141414</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B63">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C63" s="65">
-        <v>123456789</v>
-      </c>
-      <c t="n" r="D63">
-        <v>1</v>
+          <t xml:space="preserve">15/01</t>
+        </is>
+      </c>
+      <c r="B63" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">15/01</t>
+        </is>
       </c>
       <c t="n" r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F63">
         <is>
@@ -2418,24 +2415,27 @@
         </is>
       </c>
       <c r="B64" s="56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">15/01</t>
-        </is>
+          <t xml:space="preserve">15/01%</t>
+        </is>
+      </c>
+      <c t="n" r="D64">
+        <v>1</v>
       </c>
       <c t="n" r="E64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
@@ -2447,16 +2447,14 @@
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">15/01</t>
+          <t xml:space="preserve">Teste 1515</t>
         </is>
       </c>
       <c r="B65" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C65">
-        <is>
-          <t xml:space="preserve">15/01%</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="C65" s="65">
+        <v>1515</v>
       </c>
       <c t="n" r="D65">
         <v>1</v>
@@ -2466,12 +2464,12 @@
       </c>
       <c t="inlineStr" r="F65">
         <is>
-          <t xml:space="preserve">15/01/2026 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t xml:space="preserve">15/01/2026 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
@@ -2483,29 +2481,28 @@
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Teste 1515</t>
-        </is>
-      </c>
-      <c r="B66" s="56">
-        <v>0.3</v>
+          <t xml:space="preserve">Teste 151515</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C66" s="65">
-        <v>1515</v>
-      </c>
-      <c t="n" r="D66">
-        <v>1</v>
+        <v>151515</v>
       </c>
       <c t="n" r="E66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
@@ -2517,7 +2514,7 @@
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Teste 151515</t>
+          <t xml:space="preserve">Teste 0115</t>
         </is>
       </c>
       <c t="inlineStr" r="B67">
@@ -2526,19 +2523,19 @@
         </is>
       </c>
       <c r="C67" s="65">
-        <v>151515</v>
+        <v>15151515</v>
       </c>
       <c t="n" r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F67">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G67">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H67">
@@ -2550,28 +2547,31 @@
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">Teste 0115</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B68">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C68" s="65">
-        <v>15151515</v>
+          <t xml:space="preserve">teste cupom 20/01</t>
+        </is>
+      </c>
+      <c r="B68" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">lc202601</t>
+        </is>
+      </c>
+      <c t="n" r="D68">
+        <v>20</v>
       </c>
       <c t="n" r="E68">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">20/01/2026 12:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">29/01/2026 18:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H68">
@@ -2583,31 +2583,29 @@
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">teste cupom 20/01</t>
+          <t xml:space="preserve">Teste 2101</t>
         </is>
       </c>
       <c r="B69" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C69">
-        <is>
-          <t xml:space="preserve">lc202601</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="C69" s="65">
+        <v>2101</v>
       </c>
       <c t="n" r="D69">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c t="n" r="E69">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">20/01/2026 12:40:00</t>
+          <t xml:space="preserve">21/01/2026 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">29/01/2026 18:50:00</t>
+          <t xml:space="preserve">21/01/2026 11:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
@@ -2619,14 +2617,16 @@
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Teste 2101</t>
-        </is>
-      </c>
-      <c r="B70" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C70" s="65">
-        <v>2101</v>
+        <v>21012</v>
       </c>
       <c t="n" r="D70">
         <v>1</v>
@@ -2636,24 +2636,24 @@
       </c>
       <c t="inlineStr" r="F70">
         <is>
-          <t xml:space="preserve">21/01/2026 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G70">
         <is>
-          <t xml:space="preserve">21/01/2026 11:35:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Teste 2</t>
+          <t xml:space="preserve">Teste 100% 2101</t>
         </is>
       </c>
       <c t="inlineStr" r="B71">
@@ -2662,13 +2662,10 @@
         </is>
       </c>
       <c r="C71" s="65">
-        <v>21012</v>
-      </c>
-      <c t="n" r="D71">
-        <v>1</v>
+        <v>2006</v>
       </c>
       <c t="n" r="E71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F71">
         <is>
@@ -2682,26 +2679,24 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">Teste 100% 2101</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B72">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Teste 21013</t>
+        </is>
+      </c>
+      <c r="B72" s="56">
+        <v>0.5</v>
       </c>
       <c r="C72" s="65">
-        <v>2006</v>
+        <v>21013</v>
       </c>
       <c t="n" r="E72">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F72">
         <is>
@@ -2722,26 +2717,31 @@
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">Teste 21013</t>
+          <t xml:space="preserve">cupom teste 21/01</t>
         </is>
       </c>
       <c r="B73" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C73" s="65">
-        <v>21013</v>
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">my20261</t>
+        </is>
+      </c>
+      <c t="n" r="D73">
+        <v>11</v>
       </c>
       <c t="n" r="E73">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 13:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
@@ -2753,7 +2753,7 @@
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">cupom teste 21/01</t>
+          <t xml:space="preserve">cupom porcentagem</t>
         </is>
       </c>
       <c r="B74" s="56">
@@ -2761,23 +2761,23 @@
       </c>
       <c t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">my20261</t>
+          <t xml:space="preserve">desconto30</t>
         </is>
       </c>
       <c t="n" r="D74">
         <v>11</v>
       </c>
       <c t="n" r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">21/01/2026 13:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">21/01/2026 13:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
@@ -2789,7 +2789,7 @@
     <row r="75">
       <c t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">cupom porcentagem</t>
+          <t xml:space="preserve">cupom3030desconto</t>
         </is>
       </c>
       <c r="B75" s="56">
@@ -2797,14 +2797,14 @@
       </c>
       <c t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">desconto30</t>
+          <t xml:space="preserve">desconto30%</t>
         </is>
       </c>
       <c t="n" r="D75">
         <v>11</v>
       </c>
       <c t="n" r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F75">
         <is>
@@ -2825,22 +2825,19 @@
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">cupom3030desconto</t>
-        </is>
-      </c>
-      <c r="B76" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C76">
-        <is>
-          <t xml:space="preserve">desconto30%</t>
-        </is>
-      </c>
-      <c t="n" r="D76">
-        <v>11</v>
+          <t xml:space="preserve">Teste Metade 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C76" s="65">
+        <v>2201</v>
       </c>
       <c t="n" r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F76">
         <is>
@@ -2861,19 +2858,17 @@
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Teste Metade 1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B77">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Valor Minimo 2</t>
+        </is>
+      </c>
+      <c r="B77" s="56">
+        <v>0.01</v>
       </c>
       <c r="C77" s="65">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c t="n" r="E77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F77">
         <is>
@@ -2887,21 +2882,21 @@
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 3.00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">Valor Minimo 2</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B78" s="56">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="C78" s="65">
-        <v>2203</v>
+        <v>5656</v>
       </c>
       <c t="n" r="E78">
         <v>0</v>
@@ -2918,99 +2913,99 @@
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">R$ 3.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c t="inlineStr" r="A79">
-        <is>
-          <t xml:space="preserve">teste</t>
-        </is>
+      <c r="A79" s="65">
+        <v>2601</v>
       </c>
       <c r="B79" s="56">
         <v>0.5</v>
       </c>
       <c r="C79" s="65">
-        <v>5656</v>
+        <v>2601</v>
+      </c>
+      <c t="n" r="D79">
+        <v>1</v>
       </c>
       <c t="n" r="E79">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G79">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H79">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="65">
-        <v>2601</v>
+      <c t="inlineStr" r="A80">
+        <is>
+          <t xml:space="preserve">2601-1</t>
+        </is>
       </c>
       <c r="B80" s="56">
         <v>0.5</v>
       </c>
       <c r="C80" s="65">
-        <v>2601</v>
+        <v>26011</v>
       </c>
       <c t="n" r="D80">
         <v>1</v>
       </c>
       <c t="n" r="E80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">26/01/2026 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G80">
         <is>
-          <t xml:space="preserve">26/01/2026 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">2601-1</t>
+          <t xml:space="preserve">2601-2</t>
         </is>
       </c>
       <c r="B81" s="56">
-        <v>0.5</v>
+        <v>260.12</v>
       </c>
       <c r="C81" s="65">
-        <v>26011</v>
-      </c>
-      <c t="n" r="D81">
-        <v>1</v>
+        <v>26012</v>
       </c>
       <c t="n" r="E81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G81">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H81">
@@ -3020,28 +3015,28 @@
       </c>
     </row>
     <row r="82">
-      <c t="inlineStr" r="A82">
-        <is>
-          <t xml:space="preserve">2601-2</t>
-        </is>
-      </c>
-      <c r="B82" s="56">
-        <v>260.12</v>
+      <c r="A82" s="65">
+        <v>26013</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C82" s="65">
-        <v>26012</v>
+        <v>26013</v>
       </c>
       <c t="n" r="E82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F82">
         <is>
-          <t xml:space="preserve">26/01/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G82">
         <is>
-          <t xml:space="preserve">26/01/2026 11:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H82">
@@ -3051,28 +3046,33 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="65">
-        <v>26013</v>
-      </c>
-      <c t="inlineStr" r="B83">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C83" s="65">
-        <v>26013</v>
+      <c t="inlineStr" r="A83">
+        <is>
+          <t xml:space="preserve">cupom 27/01 checklist</t>
+        </is>
+      </c>
+      <c r="B83" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">semogoiac</t>
+        </is>
+      </c>
+      <c t="n" r="D83">
+        <v>2</v>
       </c>
       <c t="n" r="E83">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
@@ -3084,31 +3084,28 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">cupom 27/01 checklist</t>
+          <t xml:space="preserve">LECTOR10</t>
         </is>
       </c>
       <c r="B84" s="56">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">semogoiac</t>
-        </is>
-      </c>
-      <c t="n" r="D84">
-        <v>2</v>
+          <t xml:space="preserve">LECTOR10</t>
+        </is>
       </c>
       <c t="n" r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">27/01/2026 11:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">27/01/2026 11:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
@@ -3120,7 +3117,7 @@
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">LECTOR10</t>
+          <t xml:space="preserve">0602 Teste</t>
         </is>
       </c>
       <c r="B85" s="56">
@@ -3128,32 +3125,35 @@
       </c>
       <c t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">LECTOR10</t>
-        </is>
+          <t xml:space="preserve">0602</t>
+        </is>
+      </c>
+      <c t="n" r="D85">
+        <v>1</v>
       </c>
       <c t="n" r="E85">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">0602 Teste</t>
+          <t xml:space="preserve">Teste 0602</t>
         </is>
       </c>
       <c r="B86" s="56">
@@ -3161,47 +3161,46 @@
       </c>
       <c t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">0602</t>
+          <t xml:space="preserve">0602-1</t>
         </is>
       </c>
       <c t="n" r="D86">
         <v>1</v>
       </c>
       <c t="n" r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">06/02/2026 11:50:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G86">
         <is>
-          <t xml:space="preserve">06/02/2026 11:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">Teste 0602</t>
-        </is>
-      </c>
-      <c r="B87" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">0602-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">0602-1</t>
-        </is>
-      </c>
-      <c t="n" r="D87">
-        <v>1</v>
+          <t xml:space="preserve">0602-3</t>
+        </is>
       </c>
       <c t="n" r="E87">
         <v>1</v>
@@ -3225,21 +3224,22 @@
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">0602-1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B88">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">cupomluiz</t>
+        </is>
+      </c>
+      <c r="B88" s="56">
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">0602-3</t>
-        </is>
+          <t xml:space="preserve">luiz100</t>
+        </is>
+      </c>
+      <c t="n" r="D88">
+        <v>100</v>
       </c>
       <c t="n" r="E88">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c t="inlineStr" r="F88">
         <is>
@@ -3260,22 +3260,20 @@
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">cupomluiz</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B89" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C89">
-        <is>
-          <t xml:space="preserve">luiz100</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="C89" s="65">
+        <v>1602</v>
       </c>
       <c t="n" r="D89">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E89">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F89">
         <is>
@@ -3296,14 +3294,14 @@
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">Teste 1602</t>
         </is>
       </c>
       <c r="B90" s="56">
         <v>0.5</v>
       </c>
       <c r="C90" s="65">
-        <v>1602</v>
+        <v>16021</v>
       </c>
       <c t="n" r="D90">
         <v>1</v>
@@ -3313,12 +3311,12 @@
       </c>
       <c t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">16/02/2026 17:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">16/02/2026 23:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
@@ -3330,29 +3328,28 @@
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Teste 1602</t>
-        </is>
-      </c>
-      <c r="B91" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 1602 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C91" s="65">
-        <v>16021</v>
-      </c>
-      <c t="n" r="D91">
-        <v>1</v>
+        <v>16022</v>
       </c>
       <c t="n" r="E91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">16/02/2026 17:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">16/02/2026 23:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
@@ -3364,19 +3361,19 @@
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">Teste 1602 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B92">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C92" s="65">
-        <v>16022</v>
+          <t xml:space="preserve">teste cupom</t>
+        </is>
+      </c>
+      <c r="B92" s="56">
+        <v>0.11</v>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">codigo10teste</t>
+        </is>
       </c>
       <c t="n" r="E92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F92">
         <is>
@@ -3397,28 +3394,29 @@
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">teste cupom</t>
+          <t xml:space="preserve">Cupom Cypress</t>
         </is>
       </c>
       <c r="B93" s="56">
-        <v>0.11</v>
-      </c>
-      <c t="inlineStr" r="C93">
-        <is>
-          <t xml:space="preserve">codigo10teste</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="C93" s="65">
+        <v>808182</v>
+      </c>
+      <c t="n" r="D93">
+        <v>80</v>
       </c>
       <c t="n" r="E93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/01/2026 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/12/2026 18:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
@@ -3430,100 +3428,99 @@
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Cupom Cypress</t>
-        </is>
-      </c>
-      <c r="B94" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Valor Minimo 3</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C94" s="65">
-        <v>808182</v>
-      </c>
-      <c t="n" r="D94">
-        <v>80</v>
+        <v>1901</v>
       </c>
       <c t="n" r="E94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">01/01/2026 10:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G94">
         <is>
-          <t xml:space="preserve">05/12/2026 18:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H94">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 100.00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">Valor Minimo 3</t>
+          <t xml:space="preserve">cupom10trilha</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C95" s="65">
-        <v>1901</v>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">cupom10trilha</t>
+        </is>
+      </c>
+      <c t="n" r="D95">
+        <v>5</v>
       </c>
       <c t="n" r="E95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23/02/2026 17:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23/02/2026 17:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">R$ 100.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">cupom10trilha</t>
+          <t xml:space="preserve">Teste100</t>
         </is>
       </c>
       <c t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C96">
-        <is>
-          <t xml:space="preserve">cupom10trilha</t>
-        </is>
-      </c>
-      <c t="n" r="D96">
-        <v>5</v>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C96" s="65">
+        <v>99</v>
       </c>
       <c t="n" r="E96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">23/02/2026 17:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">23/02/2026 17:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
@@ -3535,19 +3532,17 @@
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Teste100</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B97">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Teste 200</t>
+        </is>
+      </c>
+      <c r="B97" s="56">
+        <v>0.5</v>
       </c>
       <c r="C97" s="65">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c t="n" r="E97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F97">
         <is>
@@ -3568,26 +3563,26 @@
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">Teste 200</t>
+          <t xml:space="preserve">expirado</t>
         </is>
       </c>
       <c r="B98" s="56">
         <v>0.5</v>
       </c>
       <c r="C98" s="65">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c t="n" r="E98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24/02/2026 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">24/02/2026 10:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
@@ -3599,26 +3594,26 @@
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">expirado</t>
+          <t xml:space="preserve">teste 3</t>
         </is>
       </c>
       <c r="B99" s="56">
         <v>0.5</v>
       </c>
       <c r="C99" s="65">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c t="n" r="E99">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">24/02/2026 10:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">24/02/2026 10:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
@@ -3630,17 +3625,22 @@
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">teste 3</t>
-        </is>
-      </c>
-      <c r="B100" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">teste 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C100" s="65">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c t="n" r="D100">
+        <v>1</v>
       </c>
       <c t="n" r="E100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F100">
         <is>
@@ -3661,7 +3661,7 @@
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">teste 1</t>
+          <t xml:space="preserve">Vencido</t>
         </is>
       </c>
       <c t="inlineStr" r="B101">
@@ -3670,10 +3670,7 @@
         </is>
       </c>
       <c r="C101" s="65">
-        <v>44</v>
-      </c>
-      <c t="n" r="D101">
-        <v>1</v>
+        <v>202020</v>
       </c>
       <c t="n" r="E101">
         <v>1</v>
@@ -3697,7 +3694,7 @@
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Vencido</t>
+          <t xml:space="preserve">Real 1</t>
         </is>
       </c>
       <c t="inlineStr" r="B102">
@@ -3706,10 +3703,10 @@
         </is>
       </c>
       <c r="C102" s="65">
-        <v>202020</v>
+        <v>303030</v>
       </c>
       <c t="n" r="E102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F102">
         <is>
@@ -3730,7 +3727,7 @@
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Real 1</t>
+          <t xml:space="preserve">Real 2</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
@@ -3739,10 +3736,13 @@
         </is>
       </c>
       <c r="C103" s="65">
-        <v>303030</v>
+        <v>404040</v>
+      </c>
+      <c t="n" r="D103">
+        <v>1</v>
       </c>
       <c t="n" r="E103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F103">
         <is>
@@ -3763,19 +3763,14 @@
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Real 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B104">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Porcentagem</t>
+        </is>
+      </c>
+      <c r="B104" s="56">
+        <v>0.5</v>
       </c>
       <c r="C104" s="65">
-        <v>404040</v>
-      </c>
-      <c t="n" r="D104">
-        <v>1</v>
+        <v>707070</v>
       </c>
       <c t="n" r="E104">
         <v>1</v>
@@ -3799,17 +3794,17 @@
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Porcentagem</t>
+          <t xml:space="preserve">Valor minimo</t>
         </is>
       </c>
       <c r="B105" s="56">
         <v>0.5</v>
       </c>
       <c r="C105" s="65">
-        <v>707070</v>
+        <v>909090</v>
       </c>
       <c t="n" r="E105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F105">
         <is>
@@ -3823,45 +3818,47 @@
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">Valor minimo</t>
-        </is>
-      </c>
-      <c r="B106" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">teste ext</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C106" s="65">
-        <v>909090</v>
+        <v>959595</v>
       </c>
       <c t="n" r="E106">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/02/2026 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G106">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/02/2026 09:20:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">teste ext</t>
+          <t xml:space="preserve">teste 03</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
@@ -3869,89 +3866,87 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c r="C107" s="65">
-        <v>959595</v>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">0303</t>
+        </is>
+      </c>
+      <c t="n" r="D107">
+        <v>1</v>
       </c>
       <c t="n" r="E107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">26/02/2026 09:00:00</t>
+          <t xml:space="preserve">03/03/2026 13:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G107">
         <is>
-          <t xml:space="preserve">26/02/2026 09:20:00</t>
+          <t xml:space="preserve">03/03/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">teste 03</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B108">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C108">
-        <is>
-          <t xml:space="preserve">0303</t>
-        </is>
-      </c>
-      <c t="n" r="D108">
-        <v>1</v>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c r="B108" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C108" s="65">
+        <v>330</v>
       </c>
       <c t="n" r="E108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F108">
         <is>
+          <t xml:space="preserve">03/03/2026 13:35:00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G108">
+        <is>
           <t xml:space="preserve">03/03/2026 13:40:00</t>
         </is>
       </c>
-      <c t="inlineStr" r="G108">
-        <is>
-          <t xml:space="preserve">03/03/2026 14:00:00</t>
-        </is>
-      </c>
       <c t="inlineStr" r="H108">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">expirado</t>
+          <t xml:space="preserve">teste trilha</t>
         </is>
       </c>
       <c r="B109" s="56">
         <v>0.5</v>
       </c>
       <c r="C109" s="65">
-        <v>330</v>
+        <v>61615</v>
       </c>
       <c t="n" r="E109">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">03/03/2026 13:35:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G109">
         <is>
-          <t xml:space="preserve">03/03/2026 13:40:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H109">
@@ -3963,17 +3958,17 @@
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">teste trilha</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B110" s="56">
         <v>0.5</v>
       </c>
       <c r="C110" s="65">
-        <v>61615</v>
+        <v>61617</v>
       </c>
       <c t="n" r="E110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F110">
         <is>
@@ -3994,17 +3989,19 @@
     <row r="111">
       <c t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c r="B111" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">cupom teste 12</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C111" s="65">
-        <v>61617</v>
+        <v>1203</v>
       </c>
       <c t="n" r="E111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F111">
         <is>
@@ -4025,28 +4022,29 @@
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">cupom teste 12</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B112">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">cupom teste 13</t>
+        </is>
+      </c>
+      <c r="B112" s="56">
+        <v>0.5</v>
       </c>
       <c r="C112" s="65">
-        <v>1203</v>
+        <v>1204</v>
+      </c>
+      <c t="n" r="D112">
+        <v>1</v>
       </c>
       <c t="n" r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/03/2026 08:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G112">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/03/2026 09:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H112">
@@ -4058,29 +4056,26 @@
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">cupom teste 13</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B113" s="56">
         <v>0.5</v>
       </c>
       <c r="C113" s="65">
-        <v>1204</v>
-      </c>
-      <c t="n" r="D113">
-        <v>1</v>
+        <v>1205</v>
       </c>
       <c t="n" r="E113">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">12/03/2026 08:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G113">
         <is>
-          <t xml:space="preserve">12/03/2026 09:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H113">
@@ -4092,17 +4087,17 @@
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">100% Teste</t>
         </is>
       </c>
       <c r="B114" s="56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C114" s="65">
-        <v>1205</v>
+        <v>13033</v>
       </c>
       <c t="n" r="E114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F114">
         <is>
@@ -4123,53 +4118,53 @@
     <row r="115">
       <c t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">100% Teste</t>
-        </is>
-      </c>
-      <c r="B115" s="56">
-        <v>1</v>
+          <t xml:space="preserve">Teste 1703</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C115" s="65">
-        <v>13033</v>
+        <v>17031</v>
+      </c>
+      <c t="n" r="D115">
+        <v>1</v>
       </c>
       <c t="n" r="E115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">17/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G115">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">18/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">Teste 1703</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B116">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Teste 2 1703 expirado</t>
+        </is>
+      </c>
+      <c r="B116" s="56">
+        <v>5</v>
       </c>
       <c r="C116" s="65">
-        <v>17031</v>
-      </c>
-      <c t="n" r="D116">
-        <v>1</v>
+        <v>17032</v>
       </c>
       <c t="n" r="E116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F116">
         <is>
@@ -4178,38 +4173,38 @@
       </c>
       <c t="inlineStr" r="G116">
         <is>
-          <t xml:space="preserve">18/03/2026 00:00:00</t>
+          <t xml:space="preserve">17/03/2026 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Teste 2 1703 expirado</t>
+          <t xml:space="preserve">Teste3 1703</t>
         </is>
       </c>
       <c r="B117" s="56">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="C117" s="65">
-        <v>17032</v>
+        <v>17033</v>
       </c>
       <c t="n" r="E117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">17/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G117">
         <is>
-          <t xml:space="preserve">17/03/2026 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H117">
@@ -4221,17 +4216,17 @@
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">Teste3 1703</t>
+          <t xml:space="preserve">ValorAcimaDoMinimo2</t>
         </is>
       </c>
       <c r="B118" s="56">
         <v>0.5</v>
       </c>
       <c r="C118" s="65">
-        <v>17033</v>
+        <v>919293</v>
       </c>
       <c t="n" r="E118">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F118">
         <is>
@@ -4245,21 +4240,21 @@
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 50.00</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c t="inlineStr" r="A119">
-        <is>
-          <t xml:space="preserve">ValorAcimaDoMinimo2</t>
-        </is>
-      </c>
-      <c r="B119" s="56">
-        <v>0.5</v>
+      <c r="A119" s="65">
+        <v>777</v>
+      </c>
+      <c t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C119" s="65">
-        <v>919293</v>
+        <v>111225</v>
       </c>
       <c t="n" r="E119">
         <v>0</v>
@@ -4276,24 +4271,24 @@
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">R$ 50.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="65">
-        <v>777</v>
-      </c>
-      <c t="inlineStr" r="B120">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+      <c t="inlineStr" r="A120">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+      <c r="B120" s="56">
+        <v>0.5</v>
       </c>
       <c r="C120" s="65">
-        <v>111225</v>
+        <v>2025</v>
       </c>
       <c t="n" r="E120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F120">
         <is>
@@ -4314,26 +4309,29 @@
     <row r="121">
       <c t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">ok</t>
+          <t xml:space="preserve">Cupom Cypress</t>
         </is>
       </c>
       <c r="B121" s="56">
         <v>0.5</v>
       </c>
       <c r="C121" s="65">
-        <v>2025</v>
+        <v>808183</v>
+      </c>
+      <c t="n" r="D121">
+        <v>80</v>
       </c>
       <c t="n" r="E121">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/01/2026 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G121">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/12/2026 18:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H121">

--- a/cypress/downloads/Plataforma externa Volta Redonda.xlsx
+++ b/cypress/downloads/Plataforma externa Volta Redonda.xlsx
@@ -269,31 +269,33 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">Teste2306</t>
-        </is>
-      </c>
-      <c r="B3" s="56">
-        <v>0.1</v>
+          <t xml:space="preserve">Testecupom</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B3">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">teste2306</t>
+          <t xml:space="preserve">Testecupom</t>
         </is>
       </c>
       <c t="n" r="D3">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c t="n" r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">23/06/2025 15:25:00</t>
+          <t xml:space="preserve">23/09/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/09/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
@@ -305,58 +307,50 @@
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">dia17</t>
-        </is>
-      </c>
-      <c r="B4" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C4">
-        <is>
-          <t xml:space="preserve">dia17</t>
-        </is>
-      </c>
-      <c t="n" r="D4">
-        <v>100</v>
+          <t xml:space="preserve">TESTE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B4">
+        <is>
+          <t xml:space="preserve">R$ 60.00</t>
+        </is>
+      </c>
+      <c r="C4" s="65">
+        <v>606060</v>
       </c>
       <c t="n" r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">17/07/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">17/07/2025 19:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">teste08/08</t>
+          <t xml:space="preserve">TESTE</t>
         </is>
       </c>
       <c r="B5" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C5">
-        <is>
-          <t xml:space="preserve">teste08/08</t>
-        </is>
-      </c>
-      <c t="n" r="D5">
-        <v>100</v>
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="65">
+        <v>505050</v>
       </c>
       <c t="n" r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
@@ -370,37 +364,33 @@
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">testecupom</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B6">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C6">
-        <is>
-          <t xml:space="preserve">testecupom</t>
-        </is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B6" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="65">
+        <v>4040</v>
       </c>
       <c t="n" r="E6">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">20/08/2025 09:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">22/08/2025 11:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
@@ -412,19 +402,24 @@
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">testecupom21/08</t>
-        </is>
-      </c>
-      <c r="B7" s="56">
-        <v>0.1</v>
+          <t xml:space="preserve">teste2609</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B7">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">testecupom21/08</t>
-        </is>
+          <t xml:space="preserve">teste2609</t>
+        </is>
+      </c>
+      <c t="n" r="D7">
+        <v>100</v>
       </c>
       <c t="n" r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F7">
         <is>
@@ -445,31 +440,33 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">Cupom7</t>
-        </is>
-      </c>
-      <c r="B8" s="56">
-        <v>0.1</v>
+          <t xml:space="preserve">testecupom10/10</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B8">
+        <is>
+          <t xml:space="preserve">R$ 10.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">0712</t>
+          <t xml:space="preserve">testecupom10/10</t>
         </is>
       </c>
       <c t="n" r="D8">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c t="n" r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">10/10/2025 08:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">11/10/2025 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
@@ -481,17 +478,22 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">CUPOM TESTE</t>
+          <t xml:space="preserve">cupom14/10</t>
         </is>
       </c>
       <c r="B9" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="65">
-        <v>1010</v>
+        <v>0.1</v>
+      </c>
+      <c t="inlineStr" r="C9">
+        <is>
+          <t xml:space="preserve">cupom14/10</t>
+        </is>
+      </c>
+      <c t="n" r="D9">
+        <v>100</v>
       </c>
       <c t="n" r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
@@ -512,33 +514,26 @@
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">Testecupom</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B10">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C10">
-        <is>
-          <t xml:space="preserve">Testecupom</t>
-        </is>
-      </c>
-      <c t="n" r="D10">
-        <v>50</v>
+          <t xml:space="preserve">Cupom50</t>
+        </is>
+      </c>
+      <c r="B10" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="65">
+        <v>3110</v>
       </c>
       <c t="n" r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">23/09/2025 08:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">26/09/2025 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
@@ -550,81 +545,87 @@
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">TESTE</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B11">
-        <is>
-          <t xml:space="preserve">R$ 60.00</t>
-        </is>
+          <t xml:space="preserve">Teste12/11</t>
+        </is>
+      </c>
+      <c r="B11" s="56">
+        <v>0.5</v>
       </c>
       <c r="C11" s="65">
-        <v>606060</v>
+        <v>105</v>
+      </c>
+      <c t="n" r="D11">
+        <v>10</v>
       </c>
       <c t="n" r="E11">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">TESTE</t>
-        </is>
-      </c>
-      <c r="B12" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">TESTE12/11</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B12">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C12" s="65">
-        <v>505050</v>
+        <v>201</v>
+      </c>
+      <c t="n" r="D12">
+        <v>1</v>
       </c>
       <c t="n" r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">cupom502</t>
         </is>
       </c>
       <c r="B13" s="56">
         <v>0.5</v>
       </c>
       <c r="C13" s="65">
-        <v>4040</v>
+        <v>5486</v>
       </c>
       <c t="n" r="E13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -645,33 +646,29 @@
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">teste2609</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B14">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C14">
-        <is>
-          <t xml:space="preserve">teste2609</t>
-        </is>
+          <t xml:space="preserve">TESTE12/11</t>
+        </is>
+      </c>
+      <c r="B14" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="65">
+        <v>47992458811</v>
       </c>
       <c t="n" r="D14">
         <v>100</v>
       </c>
       <c t="n" r="E14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/11/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/01/2026 07:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
@@ -683,33 +680,29 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">testecupom10/10</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B15">
-        <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C15">
-        <is>
-          <t xml:space="preserve">testecupom10/10</t>
-        </is>
+          <t xml:space="preserve">Teste</t>
+        </is>
+      </c>
+      <c r="B15" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="65">
+        <v>1617</v>
       </c>
       <c t="n" r="D15">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c t="n" r="E15">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">10/10/2025 08:00:00</t>
+          <t xml:space="preserve">12/11/2025 16:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">11/10/2025 14:00:00</t>
+          <t xml:space="preserve">12/11/2025 16:20:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
@@ -721,16 +714,16 @@
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">cupom14/10</t>
-        </is>
-      </c>
-      <c r="B16" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C16">
-        <is>
-          <t xml:space="preserve">cupom14/10</t>
-        </is>
+          <t xml:space="preserve">Testeeeee</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
+      </c>
+      <c r="C16" s="65">
+        <v>2222</v>
       </c>
       <c t="n" r="D16">
         <v>100</v>
@@ -757,17 +750,19 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">Cupom50</t>
+          <t xml:space="preserve">Teste17/11</t>
         </is>
       </c>
       <c r="B17" s="56">
         <v>0.5</v>
       </c>
-      <c r="C17" s="65">
-        <v>3110</v>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Teste17/11</t>
+        </is>
       </c>
       <c t="n" r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F17">
         <is>
@@ -788,14 +783,14 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">Teste12/11</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B18" s="56">
         <v>0.5</v>
       </c>
       <c r="C18" s="65">
-        <v>105</v>
+        <v>5050</v>
       </c>
       <c t="n" r="D18">
         <v>10</v>
@@ -805,12 +800,12 @@
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">21/11/2025 14:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">01/03/2026 00:00:00</t>
+          <t xml:space="preserve">21/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
@@ -822,62 +817,67 @@
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c r="C19" s="65">
-        <v>201</v>
+        <v>123</v>
       </c>
       <c t="n" r="D19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="n" r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">18/11/2025 13:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">01/03/2026 00:00:00</t>
+          <t xml:space="preserve">19/11/2025 14:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">cupom502</t>
+          <t xml:space="preserve">testes 2111</t>
         </is>
       </c>
       <c r="B20" s="56">
         <v>0.5</v>
       </c>
-      <c r="C20" s="65">
-        <v>5486</v>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">date123</t>
+        </is>
+      </c>
+      <c t="n" r="D20">
+        <v>5</v>
       </c>
       <c t="n" r="E20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">18/11/2025 15:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">19/11/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
@@ -889,63 +889,68 @@
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">TESTE12/11</t>
-        </is>
-      </c>
-      <c r="B21" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="65">
-        <v>47992458811</v>
+          <t xml:space="preserve">Teste 04/12-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Teste 04/12-1</t>
+        </is>
       </c>
       <c t="n" r="D21">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">12/11/2025 00:00:00</t>
+          <t xml:space="preserve">04/12/2025 10:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">03/01/2026 07:35:00</t>
+          <t xml:space="preserve">04/12/2025 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B22" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="65">
-        <v>1617</v>
-      </c>
-      <c t="n" r="D22">
-        <v>100</v>
+          <t xml:space="preserve">TesteDois</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">TesteDois</t>
+        </is>
       </c>
       <c t="n" r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">12/11/2025 16:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">12/11/2025 16:20:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
@@ -957,22 +962,22 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">Testeeeee</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B23">
-        <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c r="C23" s="65">
-        <v>2222</v>
+          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
+        </is>
+      </c>
+      <c r="B23" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">limitado</t>
+        </is>
       </c>
       <c t="n" r="D23">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c t="n" r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F23">
         <is>
@@ -993,28 +998,30 @@
     <row r="24">
       <c t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">Teste17/11</t>
-        </is>
-      </c>
-      <c r="B24" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Teste17/11</t>
+          <t xml:space="preserve">acabou50</t>
         </is>
       </c>
       <c t="n" r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">04/12/2025 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
@@ -1026,41 +1033,43 @@
     <row r="25">
       <c t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">cupom teste % 08/12/2025</t>
         </is>
       </c>
       <c r="B25" s="56">
         <v>0.5</v>
       </c>
-      <c r="C25" s="65">
-        <v>5050</v>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">08122025</t>
+        </is>
       </c>
       <c t="n" r="D25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c t="n" r="E25">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">21/11/2025 14:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">21/11/2025 15:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
         </is>
       </c>
       <c t="inlineStr" r="B26">
@@ -1068,23 +1077,22 @@
           <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
-      <c r="C26" s="65">
-        <v>123</v>
-      </c>
-      <c t="n" r="D26">
-        <v>5</v>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">0802200511</t>
+        </is>
       </c>
       <c t="n" r="E26">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">18/11/2025 13:45:00</t>
+          <t xml:space="preserve">01/12/2025 04:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
         <is>
-          <t xml:space="preserve">19/11/2025 14:50:00</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H26">
@@ -1096,7 +1104,7 @@
     <row r="27">
       <c t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">testes 2111</t>
+          <t xml:space="preserve">Teste</t>
         </is>
       </c>
       <c r="B27" s="56">
@@ -1104,23 +1112,23 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">date123</t>
+          <t xml:space="preserve">0912</t>
         </is>
       </c>
       <c t="n" r="D27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">18/11/2025 15:55:00</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">19/11/2025 19:55:00</t>
+          <t xml:space="preserve">09/12/2025 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
@@ -1132,7 +1140,7 @@
     <row r="28">
       <c t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
+          <t xml:space="preserve">Teste Teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B28">
@@ -1142,7 +1150,7 @@
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Teste 04/12-1</t>
+          <t xml:space="preserve">09121</t>
         </is>
       </c>
       <c t="n" r="D28">
@@ -1153,47 +1161,47 @@
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">04/12/2025 10:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">04/12/2025 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">TesteDois</t>
+          <t xml:space="preserve">Teste 2</t>
         </is>
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">TesteDois</t>
+          <t xml:space="preserve">09122</t>
         </is>
       </c>
       <c t="n" r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 13:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
@@ -1205,15 +1213,15 @@
     <row r="30">
       <c t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">CUPOM COM LIMITE 1</t>
+          <t xml:space="preserve">cupom 09/12/25</t>
         </is>
       </c>
       <c r="B30" s="56">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">limitado</t>
+          <t xml:space="preserve">cupom101010</t>
         </is>
       </c>
       <c t="n" r="D30">
@@ -1224,24 +1232,24 @@
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">09/12/2025 19:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">expirado</t>
+          <t xml:space="preserve">cupom29929</t>
         </is>
       </c>
       <c t="inlineStr" r="B31">
@@ -1251,20 +1259,23 @@
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">acabou50</t>
-        </is>
+          <t xml:space="preserve">09082025</t>
+        </is>
+      </c>
+      <c t="n" r="D31">
+        <v>1</v>
       </c>
       <c t="n" r="E31">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">04/12/2025 13:00:00</t>
+          <t xml:space="preserve">09/12/2025 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">05/12/2025 09:00:00</t>
+          <t xml:space="preserve">09/12/2025 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
@@ -1276,31 +1287,31 @@
     <row r="32">
       <c t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">cupom teste % 08/12/2025</t>
-        </is>
-      </c>
-      <c r="B32" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C32">
-        <is>
-          <t xml:space="preserve">08122025</t>
-        </is>
+          <t xml:space="preserve">cupom data encerradda</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">R$ 5.00</t>
+        </is>
+      </c>
+      <c r="C32" s="65">
+        <v>898989</v>
       </c>
       <c t="n" r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="n" r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/11/2025 02:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">02/12/2025 01:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
@@ -1312,30 +1323,28 @@
     <row r="33">
       <c t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">cupom data expirada 08/12/2025</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B33">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">turma recorrente</t>
+        </is>
+      </c>
+      <c r="B33" s="56">
+        <v>0.1</v>
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">0802200511</t>
+          <t xml:space="preserve">teste09122025</t>
         </is>
       </c>
       <c t="n" r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">01/12/2025 04:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
@@ -1347,15 +1356,17 @@
     <row r="34">
       <c t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">Teste</t>
-        </is>
-      </c>
-      <c r="B34" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste 12/12-2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">0912</t>
+          <t xml:space="preserve">Teste 12/12-2</t>
         </is>
       </c>
       <c t="n" r="D34">
@@ -1366,12 +1377,12 @@
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">09/12/2025 15:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
@@ -1383,33 +1394,33 @@
     <row r="35">
       <c t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">Teste Teste</t>
+          <t xml:space="preserve">caio expiração teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">09121</t>
+          <t xml:space="preserve">caiocaiocaio</t>
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="n" r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/12/2025 11:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H35">
@@ -1421,7 +1432,7 @@
     <row r="36">
       <c t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">Teste 2</t>
+          <t xml:space="preserve">teste limite</t>
         </is>
       </c>
       <c t="inlineStr" r="B36">
@@ -1431,94 +1442,95 @@
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">09122</t>
-        </is>
+          <t xml:space="preserve">testelimitete</t>
+        </is>
+      </c>
+      <c t="n" r="D36">
+        <v>1</v>
       </c>
       <c t="n" r="E36">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">09/12/2025 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">09/12/2025 13:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">cupom 09/12/25</t>
+          <t xml:space="preserve">12/12 - 2</t>
         </is>
       </c>
       <c r="B37" s="56">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">cupom101010</t>
+          <t xml:space="preserve">12/12 - 2</t>
         </is>
       </c>
       <c t="n" r="D37">
         <v>1</v>
       </c>
       <c t="n" r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">09/12/2025 11:00:00</t>
+          <t xml:space="preserve">12/12/2025 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">09/12/2025 19:55:00</t>
+          <t xml:space="preserve">12/12/2025 23:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">cupom29929</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B38">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">18/12</t>
+        </is>
+      </c>
+      <c r="B38" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">09082025</t>
+          <t xml:space="preserve">18/12</t>
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c t="n" r="E38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">09/12/2025 09:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">09/12/2025 10:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
@@ -1530,55 +1542,54 @@
     <row r="39">
       <c t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">cupom data encerradda</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B39">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c r="C39" s="65">
-        <v>898989</v>
+          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
+        </is>
+      </c>
+      <c r="B39" s="56">
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">caio18122025</t>
+        </is>
       </c>
       <c t="n" r="D39">
+        <v>1</v>
+      </c>
+      <c t="n" r="E39">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="F39">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G39">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H39">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56">
+        <v>1</v>
+      </c>
+      <c r="B40" s="56">
+        <v>1</v>
+      </c>
+      <c r="C40" s="56">
+        <v>1</v>
+      </c>
+      <c t="n" r="D40">
+        <v>99</v>
+      </c>
+      <c t="n" r="E40">
         <v>2</v>
-      </c>
-      <c t="n" r="E39">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="F39">
-        <is>
-          <t xml:space="preserve">01/11/2025 02:10:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G39">
-        <is>
-          <t xml:space="preserve">02/12/2025 01:05:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H39">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c t="inlineStr" r="A40">
-        <is>
-          <t xml:space="preserve">turma recorrente</t>
-        </is>
-      </c>
-      <c r="B40" s="56">
-        <v>0.1</v>
-      </c>
-      <c t="inlineStr" r="C40">
-        <is>
-          <t xml:space="preserve">teste09122025</t>
-        </is>
-      </c>
-      <c t="n" r="E40">
-        <v>1</v>
       </c>
       <c t="inlineStr" r="F40">
         <is>
@@ -1599,21 +1610,18 @@
     <row r="41">
       <c t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
+          <t xml:space="preserve">18/12  cupom</t>
         </is>
       </c>
       <c t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 10.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Teste 12/12-2</t>
-        </is>
-      </c>
-      <c t="n" r="D41">
-        <v>1</v>
+          <t xml:space="preserve">18/12cupom</t>
+        </is>
       </c>
       <c t="n" r="E41">
         <v>1</v>
@@ -1637,33 +1645,31 @@
     <row r="42">
       <c t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">caio expiração teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B42">
-        <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
+          <t xml:space="preserve">cupom 50%</t>
+        </is>
+      </c>
+      <c r="B42" s="56">
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">caiocaiocaio</t>
+          <t xml:space="preserve">50%1812</t>
         </is>
       </c>
       <c t="n" r="D42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E42">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">12/12/2025 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">12/12/2025 11:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
@@ -1675,7 +1681,7 @@
     <row r="43">
       <c t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">teste limite</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c t="inlineStr" r="B43">
@@ -1683,13 +1689,8 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C43">
-        <is>
-          <t xml:space="preserve">testelimitete</t>
-        </is>
-      </c>
-      <c t="n" r="D43">
-        <v>1</v>
+      <c r="C43" s="65">
+        <v>969754</v>
       </c>
       <c t="n" r="E43">
         <v>0</v>
@@ -1706,14 +1707,14 @@
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
+          <t xml:space="preserve">teste metade</t>
         </is>
       </c>
       <c r="B44" s="56">
@@ -1721,23 +1722,20 @@
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">12/12 - 2</t>
-        </is>
-      </c>
-      <c t="n" r="D44">
-        <v>1</v>
+          <t xml:space="preserve">0510</t>
+        </is>
       </c>
       <c t="n" r="E44">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c t="inlineStr" r="F44">
         <is>
-          <t xml:space="preserve">12/12/2025 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">12/12/2025 23:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
@@ -1749,7 +1747,7 @@
     <row r="45">
       <c t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">TesteLimite</t>
         </is>
       </c>
       <c r="B45" s="56">
@@ -1757,14 +1755,14 @@
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">18/12</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
       <c t="n" r="D45">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c t="n" r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F45">
         <is>
@@ -1785,7 +1783,7 @@
     <row r="46">
       <c t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">Trila chefcklist 18/12/25</t>
+          <t xml:space="preserve">Data expirada</t>
         </is>
       </c>
       <c r="B46" s="56">
@@ -1793,23 +1791,20 @@
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">caio18122025</t>
-        </is>
-      </c>
-      <c t="n" r="D46">
-        <v>1</v>
+          <t xml:space="preserve">0520</t>
+        </is>
       </c>
       <c t="n" r="E46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/01/2026 14:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
@@ -1819,20 +1814,23 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="56">
-        <v>1</v>
-      </c>
-      <c r="B47" s="56">
-        <v>1</v>
-      </c>
-      <c r="C47" s="56">
-        <v>1</v>
-      </c>
-      <c t="n" r="D47">
-        <v>99</v>
+      <c t="inlineStr" r="A47">
+        <is>
+          <t xml:space="preserve">Valor Acima do minimo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">0530</t>
+        </is>
       </c>
       <c t="n" r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F47">
         <is>
@@ -1846,37 +1844,40 @@
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">18/12  cupom</t>
+          <t xml:space="preserve">teste cupom recorrente</t>
         </is>
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">18/12cupom</t>
-        </is>
+          <t xml:space="preserve">cinco reais</t>
+        </is>
+      </c>
+      <c t="n" r="D48">
+        <v>1</v>
       </c>
       <c t="n" r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/01/2026 16:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
@@ -1888,22 +1889,22 @@
     <row r="49">
       <c t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">cupom 50%</t>
+          <t xml:space="preserve">teste06/01</t>
         </is>
       </c>
       <c r="B49" s="56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">50%1812</t>
+          <t xml:space="preserve">teste06/01</t>
         </is>
       </c>
       <c t="n" r="D49">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c t="n" r="E49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F49">
         <is>
@@ -1933,10 +1934,13 @@
         </is>
       </c>
       <c r="C50" s="65">
-        <v>969754</v>
+        <v>1301</v>
+      </c>
+      <c t="n" r="D50">
+        <v>1</v>
       </c>
       <c t="n" r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F50">
         <is>
@@ -1950,26 +1954,24 @@
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">teste metade</t>
+          <t xml:space="preserve">teste2</t>
         </is>
       </c>
       <c r="B51" s="56">
         <v>0.5</v>
       </c>
-      <c t="inlineStr" r="C51">
-        <is>
-          <t xml:space="preserve">0510</t>
-        </is>
+      <c r="C51" s="65">
+        <v>1302</v>
       </c>
       <c t="n" r="E51">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F51">
         <is>
@@ -1990,22 +1992,21 @@
     <row r="52">
       <c t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">TesteLimite</t>
-        </is>
-      </c>
-      <c r="B52" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Desconto1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
-        </is>
-      </c>
-      <c t="n" r="D52">
-        <v>1</v>
+          <t xml:space="preserve">desc1</t>
+        </is>
       </c>
       <c t="n" r="E52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F52">
         <is>
@@ -2026,28 +2027,33 @@
     <row r="53">
       <c t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">Data expirada</t>
-        </is>
-      </c>
-      <c r="B53" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Desconto2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">R$ 2.00</t>
+        </is>
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">0520</t>
-        </is>
+          <t xml:space="preserve">desc2</t>
+        </is>
+      </c>
+      <c t="n" r="D53">
+        <v>10</v>
       </c>
       <c t="n" r="E53">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F53">
         <is>
-          <t xml:space="preserve">05/01/2026 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">05/01/2026 14:15:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
@@ -2059,18 +2065,17 @@
     <row r="54">
       <c t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">Valor Acima do minimo</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B54">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C54">
-        <is>
-          <t xml:space="preserve">0530</t>
-        </is>
+          <t xml:space="preserve">TesteLector14</t>
+        </is>
+      </c>
+      <c r="B54" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="C54" s="65">
+        <v>12345678</v>
+      </c>
+      <c t="n" r="D54">
+        <v>1</v>
       </c>
       <c t="n" r="E54">
         <v>1</v>
@@ -2087,40 +2092,38 @@
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">teste cupom recorrente</t>
+          <t xml:space="preserve">Teste141414</t>
         </is>
       </c>
       <c t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C55">
-        <is>
-          <t xml:space="preserve">cinco reais</t>
-        </is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C55" s="65">
+        <v>123456789</v>
       </c>
       <c t="n" r="D55">
         <v>1</v>
       </c>
       <c t="n" r="E55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">06/01/2026 15:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">06/01/2026 16:05:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
@@ -2132,22 +2135,19 @@
     <row r="56">
       <c t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">teste06/01</t>
+          <t xml:space="preserve">15/01</t>
         </is>
       </c>
       <c r="B56" s="56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">teste06/01</t>
-        </is>
-      </c>
-      <c t="n" r="D56">
-        <v>100</v>
+          <t xml:space="preserve">15/01</t>
+        </is>
       </c>
       <c t="n" r="E56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F56">
         <is>
@@ -2168,16 +2168,16 @@
     <row r="57">
       <c t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">teste</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B57">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C57" s="65">
-        <v>1301</v>
+          <t xml:space="preserve">15/01</t>
+        </is>
+      </c>
+      <c r="B57" s="56">
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">15/01%</t>
+        </is>
       </c>
       <c t="n" r="D57">
         <v>1</v>
@@ -2187,12 +2187,12 @@
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
@@ -2204,14 +2204,17 @@
     <row r="58">
       <c t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">teste2</t>
+          <t xml:space="preserve">Teste 1515</t>
         </is>
       </c>
       <c r="B58" s="56">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C58" s="65">
-        <v>1302</v>
+        <v>1515</v>
+      </c>
+      <c t="n" r="D58">
+        <v>1</v>
       </c>
       <c t="n" r="E58">
         <v>1</v>
@@ -2235,7 +2238,7 @@
     <row r="59">
       <c t="inlineStr" r="A59">
         <is>
-          <t xml:space="preserve">Desconto1</t>
+          <t xml:space="preserve">Teste 151515</t>
         </is>
       </c>
       <c t="inlineStr" r="B59">
@@ -2243,22 +2246,20 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C59">
-        <is>
-          <t xml:space="preserve">desc1</t>
-        </is>
+      <c r="C59" s="65">
+        <v>151515</v>
       </c>
       <c t="n" r="E59">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F59">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">15/01/2026 14:05:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
@@ -2270,24 +2271,19 @@
     <row r="60">
       <c t="inlineStr" r="A60">
         <is>
-          <t xml:space="preserve">Desconto2</t>
+          <t xml:space="preserve">Teste 0115</t>
         </is>
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C60">
-        <is>
-          <t xml:space="preserve">desc2</t>
-        </is>
-      </c>
-      <c t="n" r="D60">
-        <v>10</v>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C60" s="65">
+        <v>15151515</v>
       </c>
       <c t="n" r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F60">
         <is>
@@ -2308,29 +2304,31 @@
     <row r="61">
       <c t="inlineStr" r="A61">
         <is>
-          <t xml:space="preserve">TesteLector14</t>
+          <t xml:space="preserve">teste cupom 20/01</t>
         </is>
       </c>
       <c r="B61" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C61" s="65">
-        <v>12345678</v>
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">lc202601</t>
+        </is>
       </c>
       <c t="n" r="D61">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c t="n" r="E61">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F61">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">20/01/2026 12:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">29/01/2026 18:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
@@ -2342,16 +2340,14 @@
     <row r="62">
       <c t="inlineStr" r="A62">
         <is>
-          <t xml:space="preserve">Teste141414</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B62">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Teste 2101</t>
+        </is>
+      </c>
+      <c r="B62" s="56">
+        <v>0.5</v>
       </c>
       <c r="C62" s="65">
-        <v>123456789</v>
+        <v>2101</v>
       </c>
       <c t="n" r="D62">
         <v>1</v>
@@ -2361,12 +2357,12 @@
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 10:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">21/01/2026 11:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
@@ -2378,19 +2374,22 @@
     <row r="63">
       <c t="inlineStr" r="A63">
         <is>
-          <t xml:space="preserve">15/01</t>
-        </is>
-      </c>
-      <c r="B63" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C63">
-        <is>
-          <t xml:space="preserve">15/01</t>
-        </is>
+          <t xml:space="preserve">Teste 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C63" s="65">
+        <v>21012</v>
+      </c>
+      <c t="n" r="D63">
+        <v>1</v>
       </c>
       <c t="n" r="E63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F63">
         <is>
@@ -2404,38 +2403,35 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c t="inlineStr" r="A64">
         <is>
-          <t xml:space="preserve">15/01</t>
-        </is>
-      </c>
-      <c r="B64" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C64">
-        <is>
-          <t xml:space="preserve">15/01%</t>
-        </is>
-      </c>
-      <c t="n" r="D64">
-        <v>1</v>
+          <t xml:space="preserve">Teste 100% 2101</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C64" s="65">
+        <v>2006</v>
       </c>
       <c t="n" r="E64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">15/01/2026 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t xml:space="preserve">15/01/2026 14:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
@@ -2447,20 +2443,17 @@
     <row r="65">
       <c t="inlineStr" r="A65">
         <is>
-          <t xml:space="preserve">Teste 1515</t>
+          <t xml:space="preserve">Teste 21013</t>
         </is>
       </c>
       <c r="B65" s="56">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C65" s="65">
-        <v>1515</v>
-      </c>
-      <c t="n" r="D65">
-        <v>1</v>
+        <v>21013</v>
       </c>
       <c t="n" r="E65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F65">
         <is>
@@ -2481,28 +2474,31 @@
     <row r="66">
       <c t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">Teste 151515</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B66">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C66" s="65">
-        <v>151515</v>
+          <t xml:space="preserve">cupom teste 21/01</t>
+        </is>
+      </c>
+      <c r="B66" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">my20261</t>
+        </is>
+      </c>
+      <c t="n" r="D66">
+        <v>11</v>
       </c>
       <c t="n" r="E66">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">21/01/2026 13:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t xml:space="preserve">15/01/2026 14:05:00</t>
+          <t xml:space="preserve">21/01/2026 13:25:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
@@ -2514,16 +2510,19 @@
     <row r="67">
       <c t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">Teste 0115</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B67">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C67" s="65">
-        <v>15151515</v>
+          <t xml:space="preserve">cupom porcentagem</t>
+        </is>
+      </c>
+      <c r="B67" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">desconto30</t>
+        </is>
+      </c>
+      <c t="n" r="D67">
+        <v>11</v>
       </c>
       <c t="n" r="E67">
         <v>1</v>
@@ -2547,7 +2546,7 @@
     <row r="68">
       <c t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">teste cupom 20/01</t>
+          <t xml:space="preserve">cupom3030desconto</t>
         </is>
       </c>
       <c r="B68" s="56">
@@ -2555,23 +2554,23 @@
       </c>
       <c t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">lc202601</t>
+          <t xml:space="preserve">desconto30%</t>
         </is>
       </c>
       <c t="n" r="D68">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c t="n" r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F68">
         <is>
-          <t xml:space="preserve">20/01/2026 12:40:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G68">
         <is>
-          <t xml:space="preserve">29/01/2026 18:50:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H68">
@@ -2583,29 +2582,28 @@
     <row r="69">
       <c t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">Teste 2101</t>
-        </is>
-      </c>
-      <c r="B69" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Teste Metade 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C69" s="65">
-        <v>2101</v>
-      </c>
-      <c t="n" r="D69">
-        <v>1</v>
+        <v>2201</v>
       </c>
       <c t="n" r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F69">
         <is>
-          <t xml:space="preserve">21/01/2026 10:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">21/01/2026 11:35:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
@@ -2617,22 +2615,17 @@
     <row r="70">
       <c t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">Teste 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B70">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Valor Minimo 2</t>
+        </is>
+      </c>
+      <c r="B70" s="56">
+        <v>0.01</v>
       </c>
       <c r="C70" s="65">
-        <v>21012</v>
-      </c>
-      <c t="n" r="D70">
-        <v>1</v>
+        <v>2203</v>
       </c>
       <c t="n" r="E70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F70">
         <is>
@@ -2646,26 +2639,24 @@
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 3.00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">Teste 100% 2101</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B71">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B71" s="56">
+        <v>0.5</v>
       </c>
       <c r="C71" s="65">
-        <v>2006</v>
+        <v>5656</v>
       </c>
       <c t="n" r="E71">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F71">
         <is>
@@ -2684,64 +2675,63 @@
       </c>
     </row>
     <row r="72">
-      <c t="inlineStr" r="A72">
-        <is>
-          <t xml:space="preserve">Teste 21013</t>
-        </is>
+      <c r="A72" s="65">
+        <v>2601</v>
       </c>
       <c r="B72" s="56">
         <v>0.5</v>
       </c>
       <c r="C72" s="65">
-        <v>21013</v>
+        <v>2601</v>
+      </c>
+      <c t="n" r="D72">
+        <v>1</v>
       </c>
       <c t="n" r="E72">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F72">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G72">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 12:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">cupom teste 21/01</t>
+          <t xml:space="preserve">2601-1</t>
         </is>
       </c>
       <c r="B73" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C73">
-        <is>
-          <t xml:space="preserve">my20261</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="C73" s="65">
+        <v>26011</v>
       </c>
       <c t="n" r="D73">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c t="n" r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F73">
         <is>
-          <t xml:space="preserve">21/01/2026 13:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t xml:space="preserve">21/01/2026 13:25:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
@@ -2753,31 +2743,26 @@
     <row r="74">
       <c t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">cupom porcentagem</t>
+          <t xml:space="preserve">2601-2</t>
         </is>
       </c>
       <c r="B74" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C74">
-        <is>
-          <t xml:space="preserve">desconto30</t>
-        </is>
-      </c>
-      <c t="n" r="D74">
-        <v>11</v>
+        <v>260.12</v>
+      </c>
+      <c r="C74" s="65">
+        <v>26012</v>
       </c>
       <c t="n" r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">26/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
@@ -2787,24 +2772,19 @@
       </c>
     </row>
     <row r="75">
-      <c t="inlineStr" r="A75">
-        <is>
-          <t xml:space="preserve">cupom3030desconto</t>
-        </is>
-      </c>
-      <c r="B75" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C75">
-        <is>
-          <t xml:space="preserve">desconto30%</t>
-        </is>
-      </c>
-      <c t="n" r="D75">
-        <v>11</v>
+      <c r="A75" s="65">
+        <v>26013</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C75" s="65">
+        <v>26013</v>
       </c>
       <c t="n" r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F75">
         <is>
@@ -2825,28 +2805,31 @@
     <row r="76">
       <c t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">Teste Metade 1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B76">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C76" s="65">
-        <v>2201</v>
+          <t xml:space="preserve">cupom 27/01 checklist</t>
+        </is>
+      </c>
+      <c r="B76" s="56">
+        <v>0.3</v>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">semogoiac</t>
+        </is>
+      </c>
+      <c t="n" r="D76">
+        <v>2</v>
       </c>
       <c t="n" r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">27/01/2026 11:15:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
@@ -2858,14 +2841,16 @@
     <row r="77">
       <c t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">Valor Minimo 2</t>
+          <t xml:space="preserve">LECTOR10</t>
         </is>
       </c>
       <c r="B77" s="56">
-        <v>0.01</v>
-      </c>
-      <c r="C77" s="65">
-        <v>2203</v>
+        <v>0.5</v>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">LECTOR10</t>
+        </is>
       </c>
       <c t="n" r="E77">
         <v>0</v>
@@ -2882,87 +2867,97 @@
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">R$ 3.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">0602 Teste</t>
         </is>
       </c>
       <c r="B78" s="56">
         <v>0.5</v>
       </c>
-      <c r="C78" s="65">
-        <v>5656</v>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">0602</t>
+        </is>
+      </c>
+      <c t="n" r="D78">
+        <v>1</v>
       </c>
       <c t="n" r="E78">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:50:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G78">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">06/02/2026 11:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="65">
-        <v>2601</v>
+      <c t="inlineStr" r="A79">
+        <is>
+          <t xml:space="preserve">Teste 0602</t>
+        </is>
       </c>
       <c r="B79" s="56">
         <v>0.5</v>
       </c>
-      <c r="C79" s="65">
-        <v>2601</v>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">0602-1</t>
+        </is>
       </c>
       <c t="n" r="D79">
         <v>1</v>
       </c>
       <c t="n" r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">26/01/2026 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G79">
         <is>
-          <t xml:space="preserve">26/01/2026 12:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H79">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">2601-1</t>
-        </is>
-      </c>
-      <c r="B80" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C80" s="65">
-        <v>26011</v>
-      </c>
-      <c t="n" r="D80">
-        <v>1</v>
+          <t xml:space="preserve">0602-1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">0602-3</t>
+        </is>
       </c>
       <c t="n" r="E80">
         <v>1</v>
@@ -2986,26 +2981,31 @@
     <row r="81">
       <c t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">2601-2</t>
+          <t xml:space="preserve">cupomluiz</t>
         </is>
       </c>
       <c r="B81" s="56">
-        <v>260.12</v>
-      </c>
-      <c r="C81" s="65">
-        <v>26012</v>
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">luiz100</t>
+        </is>
+      </c>
+      <c t="n" r="D81">
+        <v>100</v>
       </c>
       <c t="n" r="E81">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">26/01/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G81">
         <is>
-          <t xml:space="preserve">26/01/2026 11:10:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H81">
@@ -3015,16 +3015,19 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="65">
-        <v>26013</v>
-      </c>
-      <c t="inlineStr" r="B82">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+      <c t="inlineStr" r="A82">
+        <is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B82" s="56">
+        <v>0.5</v>
       </c>
       <c r="C82" s="65">
-        <v>26013</v>
+        <v>1602</v>
+      </c>
+      <c t="n" r="D82">
+        <v>1</v>
       </c>
       <c t="n" r="E82">
         <v>1</v>
@@ -3048,31 +3051,29 @@
     <row r="83">
       <c t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">cupom 27/01 checklist</t>
+          <t xml:space="preserve">Teste 1602</t>
         </is>
       </c>
       <c r="B83" s="56">
-        <v>0.3</v>
-      </c>
-      <c t="inlineStr" r="C83">
-        <is>
-          <t xml:space="preserve">semogoiac</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="C83" s="65">
+        <v>16021</v>
       </c>
       <c t="n" r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="n" r="E83">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">27/01/2026 11:10:00</t>
+          <t xml:space="preserve">16/02/2026 17:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">27/01/2026 11:15:00</t>
+          <t xml:space="preserve">16/02/2026 23:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
@@ -3084,19 +3085,19 @@
     <row r="84">
       <c t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">LECTOR10</t>
-        </is>
-      </c>
-      <c r="B84" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C84">
-        <is>
-          <t xml:space="preserve">LECTOR10</t>
-        </is>
+          <t xml:space="preserve">Teste 1602 2</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C84" s="65">
+        <v>16022</v>
       </c>
       <c t="n" r="E84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F84">
         <is>
@@ -3117,58 +3118,52 @@
     <row r="85">
       <c t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">0602 Teste</t>
+          <t xml:space="preserve">teste cupom</t>
         </is>
       </c>
       <c r="B85" s="56">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">0602</t>
-        </is>
-      </c>
-      <c t="n" r="D85">
-        <v>1</v>
+          <t xml:space="preserve">codigo10teste</t>
+        </is>
       </c>
       <c t="n" r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">06/02/2026 11:50:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">06/02/2026 11:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">Teste 0602</t>
-        </is>
-      </c>
-      <c r="B86" s="56">
-        <v>0.5</v>
-      </c>
-      <c t="inlineStr" r="C86">
-        <is>
-          <t xml:space="preserve">0602-1</t>
-        </is>
-      </c>
-      <c t="n" r="D86">
-        <v>1</v>
+          <t xml:space="preserve">Valor Minimo 3</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C86" s="65">
+        <v>1901</v>
       </c>
       <c t="n" r="E86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F86">
         <is>
@@ -3182,37 +3177,40 @@
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 100.00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">0602-1</t>
+          <t xml:space="preserve">cupom10trilha</t>
         </is>
       </c>
       <c t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 10.00</t>
         </is>
       </c>
       <c t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">0602-3</t>
-        </is>
+          <t xml:space="preserve">cupom10trilha</t>
+        </is>
+      </c>
+      <c t="n" r="D87">
+        <v>5</v>
       </c>
       <c t="n" r="E87">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23/02/2026 17:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G87">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">23/02/2026 17:55:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H87">
@@ -3224,22 +3222,19 @@
     <row r="88">
       <c t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">cupomluiz</t>
-        </is>
-      </c>
-      <c r="B88" s="56">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="C88">
-        <is>
-          <t xml:space="preserve">luiz100</t>
-        </is>
-      </c>
-      <c t="n" r="D88">
-        <v>100</v>
+          <t xml:space="preserve">Teste100</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C88" s="65">
+        <v>99</v>
       </c>
       <c t="n" r="E88">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F88">
         <is>
@@ -3260,20 +3255,17 @@
     <row r="89">
       <c t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">Teste 200</t>
         </is>
       </c>
       <c r="B89" s="56">
         <v>0.5</v>
       </c>
       <c r="C89" s="65">
-        <v>1602</v>
-      </c>
-      <c t="n" r="D89">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c t="n" r="E89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F89">
         <is>
@@ -3294,29 +3286,26 @@
     <row r="90">
       <c t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">Teste 1602</t>
+          <t xml:space="preserve">expirado</t>
         </is>
       </c>
       <c r="B90" s="56">
         <v>0.5</v>
       </c>
       <c r="C90" s="65">
-        <v>16021</v>
-      </c>
-      <c t="n" r="D90">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c t="n" r="E90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">16/02/2026 17:00:00</t>
+          <t xml:space="preserve">24/02/2026 10:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">16/02/2026 23:00:00</t>
+          <t xml:space="preserve">24/02/2026 10:10:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
@@ -3328,19 +3317,17 @@
     <row r="91">
       <c t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">Teste 1602 2</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B91">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste 3</t>
+        </is>
+      </c>
+      <c r="B91" s="56">
+        <v>0.5</v>
       </c>
       <c r="C91" s="65">
-        <v>16022</v>
+        <v>55</v>
       </c>
       <c t="n" r="E91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F91">
         <is>
@@ -3361,16 +3348,19 @@
     <row r="92">
       <c t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">teste cupom</t>
-        </is>
-      </c>
-      <c r="B92" s="56">
-        <v>0.11</v>
-      </c>
-      <c t="inlineStr" r="C92">
-        <is>
-          <t xml:space="preserve">codigo10teste</t>
-        </is>
+          <t xml:space="preserve">teste 1</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C92" s="65">
+        <v>44</v>
+      </c>
+      <c t="n" r="D92">
+        <v>1</v>
       </c>
       <c t="n" r="E92">
         <v>1</v>
@@ -3394,29 +3384,28 @@
     <row r="93">
       <c t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">Cupom Cypress</t>
-        </is>
-      </c>
-      <c r="B93" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">Vencido</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C93" s="65">
-        <v>808182</v>
-      </c>
-      <c t="n" r="D93">
-        <v>80</v>
+        <v>202020</v>
       </c>
       <c t="n" r="E93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">01/01/2026 10:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">05/12/2026 18:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
@@ -3428,7 +3417,7 @@
     <row r="94">
       <c t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">Valor Minimo 3</t>
+          <t xml:space="preserve">Real 1</t>
         </is>
       </c>
       <c t="inlineStr" r="B94">
@@ -3437,10 +3426,10 @@
         </is>
       </c>
       <c r="C94" s="65">
-        <v>1901</v>
+        <v>303030</v>
       </c>
       <c t="n" r="E94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F94">
         <is>
@@ -3454,40 +3443,38 @@
       </c>
       <c t="inlineStr" r="H94">
         <is>
-          <t xml:space="preserve">R$ 100.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">cupom10trilha</t>
+          <t xml:space="preserve">Real 2</t>
         </is>
       </c>
       <c t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">R$ 10.00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="C95">
-        <is>
-          <t xml:space="preserve">cupom10trilha</t>
-        </is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c r="C95" s="65">
+        <v>404040</v>
       </c>
       <c t="n" r="D95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c t="n" r="E95">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">23/02/2026 17:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">23/02/2026 17:55:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
@@ -3499,19 +3486,17 @@
     <row r="96">
       <c t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">Teste100</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B96">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">Porcentagem</t>
+        </is>
+      </c>
+      <c r="B96" s="56">
+        <v>0.5</v>
       </c>
       <c r="C96" s="65">
-        <v>99</v>
+        <v>707070</v>
       </c>
       <c t="n" r="E96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F96">
         <is>
@@ -3532,17 +3517,17 @@
     <row r="97">
       <c t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">Teste 200</t>
+          <t xml:space="preserve">Valor minimo</t>
         </is>
       </c>
       <c r="B97" s="56">
         <v>0.5</v>
       </c>
       <c r="C97" s="65">
-        <v>88</v>
+        <v>909090</v>
       </c>
       <c t="n" r="E97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F97">
         <is>
@@ -3556,33 +3541,35 @@
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 5.00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">expirado</t>
-        </is>
-      </c>
-      <c r="B98" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">teste ext</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C98" s="65">
-        <v>77</v>
+        <v>959595</v>
       </c>
       <c t="n" r="E98">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">24/02/2026 10:00:00</t>
+          <t xml:space="preserve">26/02/2026 09:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">24/02/2026 10:10:00</t>
+          <t xml:space="preserve">26/02/2026 09:20:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
@@ -3594,62 +3581,64 @@
     <row r="99">
       <c t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">teste 3</t>
-        </is>
-      </c>
-      <c r="B99" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C99" s="65">
-        <v>55</v>
+          <t xml:space="preserve">teste 03</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">0303</t>
+        </is>
+      </c>
+      <c t="n" r="D99">
+        <v>1</v>
       </c>
       <c t="n" r="E99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/03/2026 13:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/03/2026 14:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">teste 1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B100">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">expirado</t>
+        </is>
+      </c>
+      <c r="B100" s="56">
+        <v>0.5</v>
       </c>
       <c r="C100" s="65">
-        <v>44</v>
-      </c>
-      <c t="n" r="D100">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c t="n" r="E100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/03/2026 13:35:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G100">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">03/03/2026 13:40:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H100">
@@ -3661,19 +3650,17 @@
     <row r="101">
       <c t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">Vencido</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B101">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste trilha</t>
+        </is>
+      </c>
+      <c r="B101" s="56">
+        <v>0.5</v>
       </c>
       <c r="C101" s="65">
-        <v>202020</v>
+        <v>61615</v>
       </c>
       <c t="n" r="E101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F101">
         <is>
@@ -3694,19 +3681,17 @@
     <row r="102">
       <c t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">Real 1</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B102">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">teste</t>
+        </is>
+      </c>
+      <c r="B102" s="56">
+        <v>0.5</v>
       </c>
       <c r="C102" s="65">
-        <v>303030</v>
+        <v>61617</v>
       </c>
       <c t="n" r="E102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F102">
         <is>
@@ -3727,7 +3712,7 @@
     <row r="103">
       <c t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">Real 2</t>
+          <t xml:space="preserve">cupom teste 12</t>
         </is>
       </c>
       <c t="inlineStr" r="B103">
@@ -3736,13 +3721,10 @@
         </is>
       </c>
       <c r="C103" s="65">
-        <v>404040</v>
-      </c>
-      <c t="n" r="D103">
-        <v>1</v>
+        <v>1203</v>
       </c>
       <c t="n" r="E103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F103">
         <is>
@@ -3763,26 +3745,29 @@
     <row r="104">
       <c t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">Porcentagem</t>
+          <t xml:space="preserve">cupom teste 13</t>
         </is>
       </c>
       <c r="B104" s="56">
         <v>0.5</v>
       </c>
       <c r="C104" s="65">
-        <v>707070</v>
+        <v>1204</v>
+      </c>
+      <c t="n" r="D104">
+        <v>1</v>
       </c>
       <c t="n" r="E104">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/03/2026 08:45:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G104">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">12/03/2026 09:30:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H104">
@@ -3794,17 +3779,17 @@
     <row r="105">
       <c t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">Valor minimo</t>
+          <t xml:space="preserve">teste</t>
         </is>
       </c>
       <c r="B105" s="56">
         <v>0.5</v>
       </c>
       <c r="C105" s="65">
-        <v>909090</v>
+        <v>1205</v>
       </c>
       <c t="n" r="E105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F105">
         <is>
@@ -3818,35 +3803,33 @@
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">R$ 5.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">teste ext</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B106">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
+          <t xml:space="preserve">100% Teste</t>
+        </is>
+      </c>
+      <c r="B106" s="56">
+        <v>1</v>
       </c>
       <c r="C106" s="65">
-        <v>959595</v>
+        <v>13033</v>
       </c>
       <c t="n" r="E106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">26/02/2026 09:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G106">
         <is>
-          <t xml:space="preserve">26/02/2026 09:20:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H106">
@@ -3858,7 +3841,7 @@
     <row r="107">
       <c t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">teste 03</t>
+          <t xml:space="preserve">Teste 1703</t>
         </is>
       </c>
       <c t="inlineStr" r="B107">
@@ -3866,10 +3849,8 @@
           <t xml:space="preserve">R$ 1.00</t>
         </is>
       </c>
-      <c t="inlineStr" r="C107">
-        <is>
-          <t xml:space="preserve">0303</t>
-        </is>
+      <c r="C107" s="65">
+        <v>17031</v>
       </c>
       <c t="n" r="D107">
         <v>1</v>
@@ -3879,43 +3860,43 @@
       </c>
       <c t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">03/03/2026 13:40:00</t>
+          <t xml:space="preserve">17/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G107">
         <is>
-          <t xml:space="preserve">03/03/2026 14:00:00</t>
+          <t xml:space="preserve">18/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">R$ 1.00</t>
+          <t xml:space="preserve">R$ 2.00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">expirado</t>
+          <t xml:space="preserve">Teste 2 1703 expirado</t>
         </is>
       </c>
       <c r="B108" s="56">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="C108" s="65">
-        <v>330</v>
+        <v>17032</v>
       </c>
       <c t="n" r="E108">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">03/03/2026 13:35:00</t>
+          <t xml:space="preserve">17/03/2026 00:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G108">
         <is>
-          <t xml:space="preserve">03/03/2026 13:40:00</t>
+          <t xml:space="preserve">17/03/2026 11:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H108">
@@ -3927,17 +3908,17 @@
     <row r="109">
       <c t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">teste trilha</t>
+          <t xml:space="preserve">Teste3 1703</t>
         </is>
       </c>
       <c r="B109" s="56">
         <v>0.5</v>
       </c>
       <c r="C109" s="65">
-        <v>61615</v>
+        <v>17033</v>
       </c>
       <c t="n" r="E109">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F109">
         <is>
@@ -3958,17 +3939,17 @@
     <row r="110">
       <c t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">ValorAcimaDoMinimo2</t>
         </is>
       </c>
       <c r="B110" s="56">
         <v>0.5</v>
       </c>
       <c r="C110" s="65">
-        <v>61617</v>
+        <v>919293</v>
       </c>
       <c t="n" r="E110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F110">
         <is>
@@ -3982,15 +3963,13 @@
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">R$ 50.00</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c t="inlineStr" r="A111">
-        <is>
-          <t xml:space="preserve">cupom teste 12</t>
-        </is>
+      <c r="A111" s="65">
+        <v>777</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3998,7 +3977,7 @@
         </is>
       </c>
       <c r="C111" s="65">
-        <v>1203</v>
+        <v>111225</v>
       </c>
       <c t="n" r="E111">
         <v>0</v>
@@ -4022,29 +4001,26 @@
     <row r="112">
       <c t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">cupom teste 13</t>
+          <t xml:space="preserve">ok</t>
         </is>
       </c>
       <c r="B112" s="56">
         <v>0.5</v>
       </c>
       <c r="C112" s="65">
-        <v>1204</v>
-      </c>
-      <c t="n" r="D112">
-        <v>1</v>
+        <v>2025</v>
       </c>
       <c t="n" r="E112">
         <v>1</v>
       </c>
       <c t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">12/03/2026 08:45:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G112">
         <is>
-          <t xml:space="preserve">12/03/2026 09:30:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H112">
@@ -4056,17 +4032,17 @@
     <row r="113">
       <c t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">teste</t>
+          <t xml:space="preserve">porcetagem20</t>
         </is>
       </c>
       <c r="B113" s="56">
         <v>0.5</v>
       </c>
       <c r="C113" s="65">
-        <v>1205</v>
+        <v>200420</v>
       </c>
       <c t="n" r="E113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F113">
         <is>
@@ -4087,17 +4063,24 @@
     <row r="114">
       <c t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">100% Teste</t>
-        </is>
-      </c>
-      <c r="B114" s="56">
-        <v>1</v>
-      </c>
-      <c r="C114" s="65">
-        <v>13033</v>
+          <t xml:space="preserve">valor 102</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">045069</t>
+        </is>
+      </c>
+      <c t="n" r="D114">
+        <v>1</v>
       </c>
       <c t="n" r="E114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F114">
         <is>
@@ -4116,10 +4099,8 @@
       </c>
     </row>
     <row r="115">
-      <c t="inlineStr" r="A115">
-        <is>
-          <t xml:space="preserve">Teste 1703</t>
-        </is>
+      <c r="A115" s="65">
+        <v>111</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -4127,53 +4108,48 @@
         </is>
       </c>
       <c r="C115" s="65">
-        <v>17031</v>
-      </c>
-      <c t="n" r="D115">
-        <v>1</v>
+        <v>1111111111</v>
       </c>
       <c t="n" r="E115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">17/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G115">
         <is>
-          <t xml:space="preserve">18/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">R$ 2.00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c t="inlineStr" r="A116">
-        <is>
-          <t xml:space="preserve">Teste 2 1703 expirado</t>
-        </is>
+      <c r="A116" s="65">
+        <v>2222</v>
       </c>
       <c r="B116" s="56">
-        <v>5</v>
+        <v>22.22</v>
       </c>
       <c r="C116" s="65">
-        <v>17032</v>
+        <v>222222</v>
       </c>
       <c t="n" r="E116">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">17/03/2026 00:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="G116">
         <is>
-          <t xml:space="preserve">17/03/2026 11:00:00</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c t="inlineStr" r="H116">
@@ -4185,17 +4161,19 @@
     <row r="117">
       <c t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">Teste3 1703</t>
-        </is>
-      </c>
-      <c r="B117" s="56">
-        <v>0.5</v>
+          <t xml:space="preserve">cupomminiteateste</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">R$ 1.00</t>
+        </is>
       </c>
       <c r="C117" s="65">
-        <v>17033</v>
+        <v>220426</v>
       </c>
       <c t="n" r="E117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F117">
         <is>
@@ -4216,125 +4194,32 @@
     <row r="118">
       <c t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">ValorAcimaDoMinimo2</t>
+          <t xml:space="preserve">Pagaamento Sicredi</t>
         </is>
       </c>
       <c r="B118" s="56">
         <v>0.5</v>
       </c>
       <c r="C118" s="65">
-        <v>919293</v>
+        <v>101112</v>
+      </c>
+      <c t="n" r="D118">
+        <v>80</v>
       </c>
       <c t="n" r="E118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">01/01/2026 07:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="G118">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">05/12/2026 15:00:00</t>
         </is>
       </c>
       <c t="inlineStr" r="H118">
-        <is>
-          <t xml:space="preserve">R$ 50.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="65">
-        <v>777</v>
-      </c>
-      <c t="inlineStr" r="B119">
-        <is>
-          <t xml:space="preserve">R$ 1.00</t>
-        </is>
-      </c>
-      <c r="C119" s="65">
-        <v>111225</v>
-      </c>
-      <c t="n" r="E119">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="F119">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G119">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H119">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c t="inlineStr" r="A120">
-        <is>
-          <t xml:space="preserve">ok</t>
-        </is>
-      </c>
-      <c r="B120" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C120" s="65">
-        <v>2025</v>
-      </c>
-      <c t="n" r="E120">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="F120">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G120">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H120">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c t="inlineStr" r="A121">
-        <is>
-          <t xml:space="preserve">Cupom Cypress</t>
-        </is>
-      </c>
-      <c r="B121" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="C121" s="65">
-        <v>808183</v>
-      </c>
-      <c t="n" r="D121">
-        <v>80</v>
-      </c>
-      <c t="n" r="E121">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="F121">
-        <is>
-          <t xml:space="preserve">01/01/2026 10:00:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G121">
-        <is>
-          <t xml:space="preserve">05/12/2026 18:00:00</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H121">
         <is>
           <t xml:space="preserve">-</t>
         </is>
